--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124938548</v>
+        <v>124937619</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,50 +1814,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446512</v>
+        <v>446452</v>
       </c>
       <c r="R11" t="n">
-        <v>7023807</v>
+        <v>7023890</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1896,7 +1896,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1911,22 +1916,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937619</v>
+        <v>124938548</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,50 +1940,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446452</v>
+        <v>446512</v>
       </c>
       <c r="R12" t="n">
-        <v>7023890</v>
+        <v>7023807</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2007,7 +2012,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2017,12 +2022,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2037,19 +2037,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124940534</v>
+        <v>124935567</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2099,14 +2099,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446314</v>
+        <v>446418</v>
       </c>
       <c r="R13" t="n">
-        <v>7023930</v>
+        <v>7023888</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2148,7 +2148,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,19 +2168,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124935567</v>
+        <v>124940534</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2210,7 +2215,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2225,14 +2230,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446418</v>
+        <v>446314</v>
       </c>
       <c r="R14" t="n">
-        <v>7023888</v>
+        <v>7023930</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -2264,7 +2269,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2274,12 +2279,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2294,12 +2294,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124938398</v>
+        <v>124940176</v>
       </c>
       <c r="B17" t="n">
-        <v>100279</v>
+        <v>79851</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2565,51 +2565,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446403</v>
+        <v>446236</v>
       </c>
       <c r="R17" t="n">
-        <v>7023878</v>
+        <v>7023806</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2638,7 +2624,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2648,12 +2634,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2668,22 +2649,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124940176</v>
+        <v>124938398</v>
       </c>
       <c r="B18" t="n">
-        <v>79851</v>
+        <v>100279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2696,37 +2677,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446236</v>
+        <v>446403</v>
       </c>
       <c r="R18" t="n">
-        <v>7023806</v>
+        <v>7023878</v>
       </c>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2755,7 +2750,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2765,7 +2760,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2780,12 +2780,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124935467</v>
+        <v>124937346</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2921,35 +2921,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2958,13 +2958,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446385</v>
+        <v>446466</v>
       </c>
       <c r="R20" t="n">
         <v>7023868</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3030,10 +3030,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124937346</v>
+        <v>124937238</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3046,46 +3046,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446466</v>
+        <v>446500</v>
       </c>
       <c r="R21" t="n">
-        <v>7023868</v>
+        <v>7023860</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3114,7 +3105,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3124,7 +3115,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3139,22 +3135,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124937238</v>
+        <v>124939729</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>98122</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3163,38 +3159,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446500</v>
+        <v>446196</v>
       </c>
       <c r="R22" t="n">
-        <v>7023860</v>
+        <v>7023847</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3226,7 +3236,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3236,12 +3246,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3268,10 +3278,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124939729</v>
+        <v>124935467</v>
       </c>
       <c r="B23" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3280,30 +3290,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3311,21 +3321,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446196</v>
+        <v>446385</v>
       </c>
       <c r="R23" t="n">
-        <v>7023847</v>
+        <v>7023868</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3357,7 +3362,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3367,12 +3372,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3387,12 +3387,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124936055</v>
+        <v>124940281</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4018,52 +4018,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446414</v>
+        <v>446268</v>
       </c>
       <c r="R29" t="n">
-        <v>7023792</v>
+        <v>7023890</v>
       </c>
       <c r="S29" t="n">
         <v>7</v>
@@ -4095,7 +4081,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4105,12 +4091,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4137,10 +4123,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124940281</v>
+        <v>124936055</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4149,38 +4135,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446268</v>
+        <v>446414</v>
       </c>
       <c r="R30" t="n">
-        <v>7023890</v>
+        <v>7023792</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124939565</v>
+        <v>124936862</v>
       </c>
       <c r="B2" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446214</v>
+        <v>446512</v>
       </c>
       <c r="R2" t="n">
-        <v>7023841</v>
+        <v>7023771</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124937577</v>
+        <v>124937238</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,55 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446475</v>
+        <v>446500</v>
       </c>
       <c r="R3" t="n">
-        <v>7023891</v>
+        <v>7023860</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124936966</v>
+        <v>124936204</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,40 +921,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446533</v>
+        <v>446448</v>
       </c>
       <c r="R4" t="n">
-        <v>7023754</v>
+        <v>7023801</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>+ 1 vinterståndare</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124937870</v>
+        <v>124939368</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,55 +1052,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446461</v>
+        <v>446236</v>
       </c>
       <c r="R5" t="n">
-        <v>7023883</v>
+        <v>7023806</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1143,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,12 +1134,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,22 +1149,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124938916</v>
+        <v>124937355</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,46 +1173,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446512</v>
+        <v>446493</v>
       </c>
       <c r="R6" t="n">
-        <v>7023807</v>
+        <v>7023830</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1265,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1275,7 +1260,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,22 +1280,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939368</v>
+        <v>124940176</v>
       </c>
       <c r="B7" t="n">
-        <v>91950</v>
+        <v>79851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1318,33 +1308,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
@@ -1357,7 +1338,7 @@
         <v>7023806</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,7 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124936204</v>
+        <v>124939729</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>98122</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1435,55 +1416,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446448</v>
+        <v>446196</v>
       </c>
       <c r="R8" t="n">
-        <v>7023801</v>
+        <v>7023847</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,7 +1493,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,12 +1503,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,22 +1523,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937032</v>
+        <v>124939441</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>95347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1566,25 +1547,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1594,13 +1575,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446505</v>
+        <v>446204</v>
       </c>
       <c r="R9" t="n">
-        <v>7023805</v>
+        <v>7023839</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1639,12 +1620,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,17 +1645,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937355</v>
+        <v>124936685</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1683,52 +1664,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446493</v>
+        <v>446500</v>
       </c>
       <c r="R10" t="n">
-        <v>7023830</v>
+        <v>7023715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,7 +1727,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1770,12 +1737,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1802,10 +1769,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937619</v>
+        <v>124938916</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,50 +1781,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446452</v>
+        <v>446512</v>
       </c>
       <c r="R11" t="n">
-        <v>7023890</v>
+        <v>7023807</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1886,7 +1849,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1896,12 +1859,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,22 +1874,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124938548</v>
+        <v>124939565</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>91700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1944,46 +1902,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446512</v>
+        <v>446214</v>
       </c>
       <c r="R12" t="n">
-        <v>7023807</v>
+        <v>7023841</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2012,7 +1961,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2022,7 +1971,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2037,7 +1991,7 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -2049,7 +2003,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124935567</v>
+        <v>124937775</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2084,7 +2038,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2092,24 +2046,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446418</v>
+        <v>446465</v>
       </c>
       <c r="R13" t="n">
-        <v>7023888</v>
+        <v>7023899</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2138,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2148,12 +2097,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2180,7 +2129,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124940534</v>
+        <v>124939030</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2215,7 +2164,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2234,13 +2183,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446314</v>
+        <v>446512</v>
       </c>
       <c r="R14" t="n">
-        <v>7023930</v>
+        <v>7023807</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2269,7 +2218,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2279,7 +2228,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2306,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124939161</v>
+        <v>124938398</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2318,25 +2267,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2346,7 +2295,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2355,13 +2309,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446288</v>
+        <v>446403</v>
       </c>
       <c r="R15" t="n">
-        <v>7023859</v>
+        <v>7023878</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2390,7 +2344,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2400,12 +2354,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2432,10 +2386,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124938507</v>
+        <v>124939668</v>
       </c>
       <c r="B16" t="n">
-        <v>91950</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2444,25 +2398,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2472,10 +2426,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446376</v>
+        <v>446191</v>
       </c>
       <c r="R16" t="n">
-        <v>7023866</v>
+        <v>7023833</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2507,7 +2461,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2517,12 +2471,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2549,10 +2503,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124940176</v>
+        <v>124937577</v>
       </c>
       <c r="B17" t="n">
-        <v>79851</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2561,41 +2515,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446236</v>
+        <v>446475</v>
       </c>
       <c r="R17" t="n">
-        <v>7023806</v>
+        <v>7023891</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2624,7 +2592,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2634,7 +2602,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2649,7 +2622,7 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2661,10 +2634,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124938398</v>
+        <v>124939161</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2673,25 +2646,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2701,12 +2674,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2715,13 +2683,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446403</v>
+        <v>446288</v>
       </c>
       <c r="R18" t="n">
-        <v>7023878</v>
+        <v>7023859</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2750,7 +2718,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2760,12 +2728,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,17 +2753,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124936198</v>
+        <v>124940534</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2804,41 +2772,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446431</v>
+        <v>446314</v>
       </c>
       <c r="R19" t="n">
-        <v>7023787</v>
+        <v>7023930</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2867,7 +2849,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2877,12 +2859,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2897,22 +2874,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124937346</v>
+        <v>124937032</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2925,46 +2902,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446466</v>
+        <v>446505</v>
       </c>
       <c r="R20" t="n">
-        <v>7023868</v>
+        <v>7023805</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2993,7 +2961,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3003,7 +2971,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3018,7 +2991,7 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -3030,10 +3003,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124937238</v>
+        <v>124936055</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3042,41 +3015,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446500</v>
+        <v>446414</v>
       </c>
       <c r="R21" t="n">
-        <v>7023860</v>
+        <v>7023792</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3105,7 +3092,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3115,12 +3102,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3147,10 +3134,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124939729</v>
+        <v>124935467</v>
       </c>
       <c r="B22" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3159,30 +3146,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3190,21 +3177,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446196</v>
+        <v>446385</v>
       </c>
       <c r="R22" t="n">
-        <v>7023847</v>
+        <v>7023868</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3236,7 +3218,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3246,12 +3228,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3266,22 +3243,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124935467</v>
+        <v>124937179</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3290,47 +3267,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446385</v>
+        <v>446500</v>
       </c>
       <c r="R23" t="n">
-        <v>7023868</v>
+        <v>7023860</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3362,7 +3330,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3372,7 +3340,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3387,22 +3360,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124939030</v>
+        <v>124938507</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3411,52 +3384,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446512</v>
+        <v>446376</v>
       </c>
       <c r="R24" t="n">
-        <v>7023807</v>
+        <v>7023866</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3488,7 +3447,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3498,7 +3457,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3513,22 +3477,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124936685</v>
+        <v>124937224</v>
       </c>
       <c r="B25" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3537,25 +3501,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3568,7 +3532,7 @@
         <v>446500</v>
       </c>
       <c r="R25" t="n">
-        <v>7023715</v>
+        <v>7023860</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3600,7 +3564,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3610,12 +3574,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3642,10 +3606,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124937775</v>
+        <v>124940260</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3654,50 +3618,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446465</v>
+        <v>446210</v>
       </c>
       <c r="R26" t="n">
-        <v>7023899</v>
+        <v>7023879</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3726,7 +3690,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3736,12 +3700,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3756,22 +3715,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124940260</v>
+        <v>124935567</v>
       </c>
       <c r="B27" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3780,50 +3739,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446210</v>
+        <v>446418</v>
       </c>
       <c r="R27" t="n">
-        <v>7023879</v>
+        <v>7023888</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3852,7 +3816,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3862,7 +3826,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3877,19 +3846,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124936862</v>
+        <v>124940281</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3929,13 +3898,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446512</v>
+        <v>446268</v>
       </c>
       <c r="R28" t="n">
-        <v>7023771</v>
+        <v>7023890</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3964,7 +3933,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3974,12 +3943,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4006,7 +3975,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124940281</v>
+        <v>124937619</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -4039,20 +4008,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446268</v>
+        <v>446452</v>
       </c>
       <c r="R29" t="n">
         <v>7023890</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4081,7 +4059,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4091,12 +4069,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4123,7 +4101,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124936055</v>
+        <v>124936966</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -4158,7 +4136,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4173,17 +4151,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446414</v>
+        <v>446533</v>
       </c>
       <c r="R30" t="n">
-        <v>7023792</v>
+        <v>7023754</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4212,7 +4190,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4222,12 +4200,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4242,7 +4220,7 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -4254,10 +4232,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124937224</v>
+        <v>124940379</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4266,38 +4244,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446500</v>
+        <v>446275</v>
       </c>
       <c r="R31" t="n">
-        <v>7023860</v>
+        <v>7023902</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4329,7 +4321,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4339,12 +4331,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4364,17 +4356,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124937179</v>
+        <v>124939540</v>
       </c>
       <c r="B32" t="n">
-        <v>77743</v>
+        <v>105102</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4383,25 +4375,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4411,10 +4403,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446500</v>
+        <v>446196</v>
       </c>
       <c r="R32" t="n">
-        <v>7023860</v>
+        <v>7023833</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4446,7 +4438,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4456,12 +4448,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4481,17 +4473,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124940379</v>
+        <v>124937346</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4500,55 +4492,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446275</v>
+        <v>446466</v>
       </c>
       <c r="R33" t="n">
-        <v>7023902</v>
+        <v>7023868</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4577,7 +4564,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4587,12 +4574,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:44</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4607,22 +4589,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124938918</v>
+        <v>124936198</v>
       </c>
       <c r="B34" t="n">
-        <v>95335</v>
+        <v>74901</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4631,25 +4613,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4659,10 +4641,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446330</v>
+        <v>446431</v>
       </c>
       <c r="R34" t="n">
-        <v>7023872</v>
+        <v>7023787</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4694,7 +4676,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4704,12 +4686,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4736,10 +4718,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124939668</v>
+        <v>124937870</v>
       </c>
       <c r="B35" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4748,38 +4730,52 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446191</v>
+        <v>446461</v>
       </c>
       <c r="R35" t="n">
-        <v>7023833</v>
+        <v>7023883</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4811,7 +4807,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4821,12 +4817,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4853,10 +4849,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124939540</v>
+        <v>124938548</v>
       </c>
       <c r="B36" t="n">
-        <v>105102</v>
+        <v>57883</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4869,37 +4865,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221725</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446196</v>
+        <v>446512</v>
       </c>
       <c r="R36" t="n">
-        <v>7023833</v>
+        <v>7023807</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4928,7 +4933,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4938,12 +4943,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4958,22 +4958,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124939441</v>
+        <v>124938918</v>
       </c>
       <c r="B37" t="n">
-        <v>95347</v>
+        <v>95335</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5010,13 +5010,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446204</v>
+        <v>446330</v>
       </c>
       <c r="R37" t="n">
-        <v>7023839</v>
+        <v>7023872</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124936862</v>
+        <v>124936204</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446512</v>
+        <v>446448</v>
       </c>
       <c r="R2" t="n">
-        <v>7023771</v>
+        <v>7023801</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +794,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124937238</v>
+        <v>124938916</v>
       </c>
       <c r="B3" t="n">
-        <v>74901</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +818,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446500</v>
+        <v>446512</v>
       </c>
       <c r="R3" t="n">
-        <v>7023860</v>
+        <v>7023807</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +911,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -909,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124936204</v>
+        <v>124940379</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,55 +935,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446448</v>
+        <v>446275</v>
       </c>
       <c r="R4" t="n">
-        <v>7023801</v>
+        <v>7023902</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1022,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,22 +1042,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124939368</v>
+        <v>124937619</v>
       </c>
       <c r="B5" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,50 +1066,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446236</v>
+        <v>446452</v>
       </c>
       <c r="R5" t="n">
-        <v>7023806</v>
+        <v>7023890</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1148,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1168,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1161,7 +1180,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124937355</v>
+        <v>124939030</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1196,7 +1215,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1211,14 +1230,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446493</v>
+        <v>446512</v>
       </c>
       <c r="R6" t="n">
-        <v>7023830</v>
+        <v>7023807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1269,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,12 +1279,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,22 +1294,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124940176</v>
+        <v>124937179</v>
       </c>
       <c r="B7" t="n">
-        <v>79851</v>
+        <v>77743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,41 +1318,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446236</v>
+        <v>446500</v>
       </c>
       <c r="R7" t="n">
-        <v>7023806</v>
+        <v>7023860</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,7 +1381,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,7 +1391,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,22 +1411,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939729</v>
+        <v>124937355</v>
       </c>
       <c r="B8" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,30 +1435,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1458,10 +1477,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446196</v>
+        <v>446493</v>
       </c>
       <c r="R8" t="n">
-        <v>7023847</v>
+        <v>7023830</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1503,12 +1522,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,10 +1554,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939441</v>
+        <v>124937032</v>
       </c>
       <c r="B9" t="n">
-        <v>95347</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1547,25 +1566,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1575,13 +1594,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446204</v>
+        <v>446505</v>
       </c>
       <c r="R9" t="n">
-        <v>7023839</v>
+        <v>7023805</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,7 +1629,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,12 +1639,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,17 +1664,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124936685</v>
+        <v>124936862</v>
       </c>
       <c r="B10" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1664,25 +1683,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1692,10 +1711,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446500</v>
+        <v>446512</v>
       </c>
       <c r="R10" t="n">
-        <v>7023715</v>
+        <v>7023771</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1727,7 +1746,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1737,12 +1756,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124938916</v>
+        <v>124935567</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,46 +1800,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446512</v>
+        <v>446418</v>
       </c>
       <c r="R11" t="n">
-        <v>7023807</v>
+        <v>7023888</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1849,7 +1877,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,7 +1887,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,22 +1907,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124939565</v>
+        <v>124937346</v>
       </c>
       <c r="B12" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1898,41 +1931,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446214</v>
+        <v>446466</v>
       </c>
       <c r="R12" t="n">
-        <v>7023841</v>
+        <v>7023868</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1961,7 +2003,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1971,12 +2013,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,7 +2028,7 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -2003,10 +2040,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124937775</v>
+        <v>124938507</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2015,47 +2052,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446465</v>
+        <v>446376</v>
       </c>
       <c r="R13" t="n">
-        <v>7023899</v>
+        <v>7023866</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,7 +2115,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,12 +2125,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2129,10 +2157,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124939030</v>
+        <v>124938548</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2141,40 +2169,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2189,7 +2212,7 @@
         <v>7023807</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2218,7 +2241,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2228,7 +2251,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2255,10 +2278,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124938398</v>
+        <v>124939161</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2267,25 +2290,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2295,12 +2318,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2309,13 +2327,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446403</v>
+        <v>446288</v>
       </c>
       <c r="R15" t="n">
-        <v>7023878</v>
+        <v>7023859</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2344,7 +2362,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2354,12 +2372,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2386,10 +2404,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124939668</v>
+        <v>124939441</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>95347</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2398,25 +2416,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>2813</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2426,13 +2444,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446191</v>
+        <v>446204</v>
       </c>
       <c r="R16" t="n">
-        <v>7023833</v>
+        <v>7023839</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2461,7 +2479,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2471,12 +2489,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2503,10 +2521,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124937577</v>
+        <v>124937238</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,55 +2533,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446475</v>
+        <v>446500</v>
       </c>
       <c r="R17" t="n">
-        <v>7023891</v>
+        <v>7023860</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2592,7 +2596,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2602,12 +2606,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2627,17 +2631,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124939161</v>
+        <v>124936198</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2650,46 +2654,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446288</v>
+        <v>446431</v>
       </c>
       <c r="R18" t="n">
-        <v>7023859</v>
+        <v>7023787</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2718,7 +2713,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2728,12 +2723,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,17 +2748,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124940534</v>
+        <v>124937224</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2772,55 +2767,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446314</v>
+        <v>446500</v>
       </c>
       <c r="R19" t="n">
-        <v>7023930</v>
+        <v>7023860</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2849,7 +2830,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2859,7 +2840,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2874,22 +2860,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124937032</v>
+        <v>124935467</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2898,38 +2884,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446505</v>
+        <v>446385</v>
       </c>
       <c r="R20" t="n">
-        <v>7023805</v>
+        <v>7023868</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2961,7 +2956,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2971,12 +2966,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2991,7 +2981,7 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -3003,10 +2993,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124936055</v>
+        <v>124939565</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3015,55 +3005,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446414</v>
+        <v>446214</v>
       </c>
       <c r="R21" t="n">
-        <v>7023792</v>
+        <v>7023841</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3092,7 +3068,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3102,12 +3078,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3134,7 +3110,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124935467</v>
+        <v>124936966</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3169,7 +3145,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3177,16 +3153,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446385</v>
+        <v>446533</v>
       </c>
       <c r="R22" t="n">
-        <v>7023868</v>
+        <v>7023754</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3218,7 +3199,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3228,7 +3209,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3255,10 +3241,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124937179</v>
+        <v>124938918</v>
       </c>
       <c r="B23" t="n">
-        <v>77743</v>
+        <v>95335</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3267,25 +3253,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3295,10 +3281,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446500</v>
+        <v>446330</v>
       </c>
       <c r="R23" t="n">
-        <v>7023860</v>
+        <v>7023872</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3330,7 +3316,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3340,12 +3326,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3365,17 +3351,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124938507</v>
+        <v>124940281</v>
       </c>
       <c r="B24" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3384,25 +3370,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3412,13 +3398,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446376</v>
+        <v>446268</v>
       </c>
       <c r="R24" t="n">
-        <v>7023866</v>
+        <v>7023890</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3447,7 +3433,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3457,12 +3443,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3489,10 +3475,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124937224</v>
+        <v>124937577</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3501,41 +3487,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446500</v>
+        <v>446475</v>
       </c>
       <c r="R25" t="n">
-        <v>7023860</v>
+        <v>7023891</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3727,10 +3727,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124935567</v>
+        <v>124939729</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3739,30 +3739,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446418</v>
+        <v>446196</v>
       </c>
       <c r="R27" t="n">
-        <v>7023888</v>
+        <v>7023847</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3858,10 +3858,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124940281</v>
+        <v>124939668</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3874,21 +3874,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3898,13 +3898,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446268</v>
+        <v>446191</v>
       </c>
       <c r="R28" t="n">
-        <v>7023890</v>
+        <v>7023833</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3975,10 +3975,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124937619</v>
+        <v>124936685</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91950</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3987,47 +3987,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446452</v>
+        <v>446500</v>
       </c>
       <c r="R29" t="n">
-        <v>7023890</v>
+        <v>7023715</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4059,7 +4050,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4069,12 +4060,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4101,10 +4092,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124936966</v>
+        <v>124940176</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>79851</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4113,55 +4104,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446533</v>
+        <v>446236</v>
       </c>
       <c r="R30" t="n">
-        <v>7023754</v>
+        <v>7023806</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4190,7 +4167,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4200,12 +4177,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:34</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>+ 1 vinterståndare</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4225,14 +4197,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124940379</v>
+        <v>124936055</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4267,7 +4239,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4286,13 +4258,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446275</v>
+        <v>446414</v>
       </c>
       <c r="R31" t="n">
-        <v>7023902</v>
+        <v>7023792</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4321,7 +4293,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4331,12 +4303,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4356,17 +4328,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124939540</v>
+        <v>124940534</v>
       </c>
       <c r="B32" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4375,41 +4347,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446196</v>
+        <v>446314</v>
       </c>
       <c r="R32" t="n">
-        <v>7023833</v>
+        <v>7023930</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4438,7 +4424,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4448,12 +4434,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4468,7 +4449,7 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -4480,10 +4461,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124937346</v>
+        <v>124937870</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4492,50 +4473,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446466</v>
+        <v>446461</v>
       </c>
       <c r="R33" t="n">
-        <v>7023868</v>
+        <v>7023883</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4564,7 +4550,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4574,7 +4560,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4589,7 +4580,7 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -4601,10 +4592,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124936198</v>
+        <v>124939368</v>
       </c>
       <c r="B34" t="n">
-        <v>74901</v>
+        <v>91950</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4613,41 +4604,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446431</v>
+        <v>446236</v>
       </c>
       <c r="R34" t="n">
-        <v>7023787</v>
+        <v>7023806</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4686,12 +4686,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4706,22 +4701,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124937870</v>
+        <v>124938398</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4730,30 +4725,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4763,7 +4758,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4772,10 +4767,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446461</v>
+        <v>446403</v>
       </c>
       <c r="R35" t="n">
-        <v>7023883</v>
+        <v>7023878</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4807,7 +4802,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4817,12 +4812,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4849,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124938548</v>
+        <v>124937775</v>
       </c>
       <c r="B36" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4861,50 +4856,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446512</v>
+        <v>446465</v>
       </c>
       <c r="R36" t="n">
-        <v>7023807</v>
+        <v>7023899</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4933,7 +4928,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4943,7 +4938,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4958,7 +4958,7 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4970,10 +4970,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124938918</v>
+        <v>124939540</v>
       </c>
       <c r="B37" t="n">
-        <v>95335</v>
+        <v>105102</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446330</v>
+        <v>446196</v>
       </c>
       <c r="R37" t="n">
-        <v>7023872</v>
+        <v>7023833</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -2157,10 +2157,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124938548</v>
+        <v>124939161</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2169,25 +2169,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2195,24 +2195,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446512</v>
+        <v>446288</v>
       </c>
       <c r="R14" t="n">
-        <v>7023807</v>
+        <v>7023859</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2251,7 +2251,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,22 +2271,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124939161</v>
+        <v>124939441</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>95347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2290,50 +2295,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446288</v>
+        <v>446204</v>
       </c>
       <c r="R15" t="n">
-        <v>7023859</v>
+        <v>7023839</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2362,7 +2358,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2372,12 +2368,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2404,10 +2400,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124939441</v>
+        <v>124937238</v>
       </c>
       <c r="B16" t="n">
-        <v>95347</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2416,25 +2412,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2813</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2444,13 +2440,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446204</v>
+        <v>446500</v>
       </c>
       <c r="R16" t="n">
-        <v>7023839</v>
+        <v>7023860</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2479,7 +2475,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2489,12 +2485,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2521,10 +2517,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124937238</v>
+        <v>124938548</v>
       </c>
       <c r="B17" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2533,41 +2529,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446500</v>
+        <v>446512</v>
       </c>
       <c r="R17" t="n">
-        <v>7023860</v>
+        <v>7023807</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2596,7 +2601,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2606,12 +2611,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2626,22 +2626,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124936198</v>
+        <v>124937224</v>
       </c>
       <c r="B18" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446431</v>
+        <v>446500</v>
       </c>
       <c r="R18" t="n">
-        <v>7023787</v>
+        <v>7023860</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2723,12 +2723,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,10 +2755,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124937224</v>
+        <v>124936198</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446500</v>
+        <v>446431</v>
       </c>
       <c r="R19" t="n">
-        <v>7023860</v>
+        <v>7023787</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124940260</v>
+        <v>124939729</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>98122</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3618,25 +3618,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3644,24 +3644,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446210</v>
+        <v>446196</v>
       </c>
       <c r="R26" t="n">
-        <v>7023879</v>
+        <v>7023847</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3690,7 +3695,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3700,7 +3705,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3715,22 +3725,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124939729</v>
+        <v>124939668</v>
       </c>
       <c r="B27" t="n">
-        <v>98122</v>
+        <v>91008</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3739,52 +3749,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446196</v>
+        <v>446191</v>
       </c>
       <c r="R27" t="n">
-        <v>7023847</v>
+        <v>7023833</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3816,7 +3812,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3826,12 +3822,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3858,10 +3854,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124939668</v>
+        <v>124940260</v>
       </c>
       <c r="B28" t="n">
-        <v>91008</v>
+        <v>57666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3874,37 +3870,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446191</v>
+        <v>446210</v>
       </c>
       <c r="R28" t="n">
-        <v>7023833</v>
+        <v>7023879</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3933,7 +3938,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3943,12 +3948,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3963,22 +3963,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124936685</v>
+        <v>124940176</v>
       </c>
       <c r="B29" t="n">
-        <v>91950</v>
+        <v>79851</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3991,37 +3991,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446500</v>
+        <v>446236</v>
       </c>
       <c r="R29" t="n">
-        <v>7023715</v>
+        <v>7023806</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4060,12 +4060,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4080,22 +4075,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124940176</v>
+        <v>124936685</v>
       </c>
       <c r="B30" t="n">
-        <v>79851</v>
+        <v>91950</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4108,37 +4103,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446236</v>
+        <v>446500</v>
       </c>
       <c r="R30" t="n">
-        <v>7023806</v>
+        <v>7023715</v>
       </c>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4167,7 +4162,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4177,7 +4172,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4192,12 +4192,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124936204</v>
+        <v>124937577</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,55 +687,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446448</v>
+        <v>446475</v>
       </c>
       <c r="R2" t="n">
-        <v>7023801</v>
+        <v>7023891</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,22 +794,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124938916</v>
+        <v>124940281</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,46 +818,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446512</v>
+        <v>446268</v>
       </c>
       <c r="R3" t="n">
-        <v>7023807</v>
+        <v>7023890</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124940379</v>
+        <v>124940534</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446275</v>
+        <v>446314</v>
       </c>
       <c r="R4" t="n">
-        <v>7023902</v>
+        <v>7023930</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,12 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:44</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,22 +1037,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124937619</v>
+        <v>124937870</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,35 +1061,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446452</v>
+        <v>446461</v>
       </c>
       <c r="R5" t="n">
-        <v>7023890</v>
+        <v>7023883</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124939030</v>
+        <v>124939565</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,52 +1192,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446512</v>
+        <v>446214</v>
       </c>
       <c r="R6" t="n">
-        <v>7023807</v>
+        <v>7023841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1269,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1279,7 +1265,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,22 +1285,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937179</v>
+        <v>124936198</v>
       </c>
       <c r="B7" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1322,21 +1313,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1346,10 +1337,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446500</v>
+        <v>446431</v>
       </c>
       <c r="R7" t="n">
-        <v>7023860</v>
+        <v>7023787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1391,12 +1382,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937355</v>
+        <v>124938918</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>95335</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1435,52 +1426,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446493</v>
+        <v>446330</v>
       </c>
       <c r="R8" t="n">
-        <v>7023830</v>
+        <v>7023872</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,12 +1499,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,10 +1531,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937032</v>
+        <v>124936204</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1570,37 +1547,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446505</v>
+        <v>446448</v>
       </c>
       <c r="R9" t="n">
-        <v>7023805</v>
+        <v>7023801</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,7 +1620,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1639,12 +1630,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,22 +1650,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124936862</v>
+        <v>124940260</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,37 +1678,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446512</v>
+        <v>446210</v>
       </c>
       <c r="R10" t="n">
-        <v>7023771</v>
+        <v>7023879</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,12 +1756,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,19 +1771,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124935567</v>
+        <v>124940379</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1823,7 +1818,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1842,13 +1837,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446418</v>
+        <v>446275</v>
       </c>
       <c r="R11" t="n">
-        <v>7023888</v>
+        <v>7023902</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1877,7 +1872,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1887,12 +1882,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1912,17 +1907,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937346</v>
+        <v>124937238</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,46 +1930,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446466</v>
+        <v>446500</v>
       </c>
       <c r="R12" t="n">
-        <v>7023868</v>
+        <v>7023860</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2003,7 +1989,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2013,7 +1999,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2028,22 +2019,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124938507</v>
+        <v>124939030</v>
       </c>
       <c r="B13" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2052,38 +2043,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446376</v>
+        <v>446512</v>
       </c>
       <c r="R13" t="n">
-        <v>7023866</v>
+        <v>7023807</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2115,7 +2120,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2125,12 +2130,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2145,22 +2145,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124939161</v>
+        <v>124938507</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2169,50 +2169,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446288</v>
+        <v>446376</v>
       </c>
       <c r="R14" t="n">
-        <v>7023859</v>
+        <v>7023866</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2241,7 +2232,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2251,12 +2242,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2283,10 +2274,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124939441</v>
+        <v>124936055</v>
       </c>
       <c r="B15" t="n">
-        <v>95347</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2295,41 +2286,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446204</v>
+        <v>446414</v>
       </c>
       <c r="R15" t="n">
-        <v>7023839</v>
+        <v>7023792</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2358,7 +2363,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2368,12 +2373,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2400,10 +2405,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124937238</v>
+        <v>124935467</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2412,38 +2417,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446500</v>
+        <v>446385</v>
       </c>
       <c r="R16" t="n">
-        <v>7023860</v>
+        <v>7023868</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2475,7 +2489,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2485,12 +2499,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2505,7 +2514,7 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2517,10 +2526,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124938548</v>
+        <v>124937179</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>77743</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2529,50 +2538,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446512</v>
+        <v>446500</v>
       </c>
       <c r="R17" t="n">
-        <v>7023807</v>
+        <v>7023860</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2611,7 +2611,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2626,22 +2631,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124937224</v>
+        <v>124939729</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98122</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2650,38 +2655,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446500</v>
+        <v>446196</v>
       </c>
       <c r="R18" t="n">
-        <v>7023860</v>
+        <v>7023847</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2713,7 +2732,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2723,12 +2742,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,10 +2774,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124936198</v>
+        <v>124937224</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2771,21 +2790,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2795,10 +2814,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446431</v>
+        <v>446500</v>
       </c>
       <c r="R19" t="n">
-        <v>7023787</v>
+        <v>7023860</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2830,7 +2849,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2840,12 +2859,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2872,10 +2891,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124935467</v>
+        <v>124936685</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,47 +2903,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446385</v>
+        <v>446500</v>
       </c>
       <c r="R20" t="n">
-        <v>7023868</v>
+        <v>7023715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2956,7 +2966,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2966,7 +2976,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2981,22 +2996,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124939565</v>
+        <v>124937355</v>
       </c>
       <c r="B21" t="n">
-        <v>91700</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3005,38 +3020,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446214</v>
+        <v>446493</v>
       </c>
       <c r="R21" t="n">
-        <v>7023841</v>
+        <v>7023830</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3068,7 +3097,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3078,12 +3107,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3234,17 +3263,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124938918</v>
+        <v>124939441</v>
       </c>
       <c r="B23" t="n">
-        <v>95335</v>
+        <v>95347</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3257,21 +3286,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3281,13 +3310,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446330</v>
+        <v>446204</v>
       </c>
       <c r="R23" t="n">
-        <v>7023872</v>
+        <v>7023839</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3316,7 +3345,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3326,12 +3355,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3351,17 +3380,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124940281</v>
+        <v>124937775</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3370,41 +3399,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446268</v>
+        <v>446465</v>
       </c>
       <c r="R24" t="n">
-        <v>7023890</v>
+        <v>7023899</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3433,7 +3471,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3443,12 +3481,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3475,7 +3513,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124937577</v>
+        <v>124935567</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3510,7 +3548,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3529,13 +3567,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446475</v>
+        <v>446418</v>
       </c>
       <c r="R25" t="n">
-        <v>7023891</v>
+        <v>7023888</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3564,7 +3602,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3574,12 +3612,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3606,10 +3644,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124939729</v>
+        <v>124939368</v>
       </c>
       <c r="B26" t="n">
-        <v>98122</v>
+        <v>91950</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3622,51 +3660,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446196</v>
+        <v>446236</v>
       </c>
       <c r="R26" t="n">
-        <v>7023847</v>
+        <v>7023806</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3695,7 +3728,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3705,12 +3738,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3725,7 +3753,7 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3737,10 +3765,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124939668</v>
+        <v>124937619</v>
       </c>
       <c r="B27" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3753,34 +3781,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446191</v>
+        <v>446452</v>
       </c>
       <c r="R27" t="n">
-        <v>7023833</v>
+        <v>7023890</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3812,7 +3849,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3822,12 +3859,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3854,10 +3891,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124940260</v>
+        <v>124940176</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>79851</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3866,50 +3903,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446210</v>
+        <v>446236</v>
       </c>
       <c r="R28" t="n">
-        <v>7023879</v>
+        <v>7023806</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3938,7 +3966,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3948,7 +3976,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3975,10 +4003,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124940176</v>
+        <v>124938548</v>
       </c>
       <c r="B29" t="n">
-        <v>79851</v>
+        <v>57883</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3991,37 +4019,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446236</v>
+        <v>446512</v>
       </c>
       <c r="R29" t="n">
-        <v>7023806</v>
+        <v>7023807</v>
       </c>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4050,7 +4087,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4060,7 +4097,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4087,10 +4124,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124936685</v>
+        <v>124937032</v>
       </c>
       <c r="B30" t="n">
-        <v>91950</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4099,25 +4136,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4127,10 +4164,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446500</v>
+        <v>446505</v>
       </c>
       <c r="R30" t="n">
-        <v>7023715</v>
+        <v>7023805</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4162,7 +4199,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4172,12 +4209,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4197,17 +4234,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124936055</v>
+        <v>124939668</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91008</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4216,55 +4253,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446414</v>
+        <v>446191</v>
       </c>
       <c r="R31" t="n">
-        <v>7023792</v>
+        <v>7023833</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4293,7 +4316,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4303,12 +4326,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,10 +4358,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124940534</v>
+        <v>124937346</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4347,40 +4370,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4389,13 +4407,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446314</v>
+        <v>446466</v>
       </c>
       <c r="R32" t="n">
-        <v>7023930</v>
+        <v>7023868</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4424,7 +4442,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4434,7 +4452,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4461,10 +4479,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124937870</v>
+        <v>124938398</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4473,30 +4491,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4506,7 +4524,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4515,10 +4533,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446461</v>
+        <v>446403</v>
       </c>
       <c r="R33" t="n">
-        <v>7023883</v>
+        <v>7023878</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4550,7 +4568,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4560,12 +4578,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4585,17 +4603,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124939368</v>
+        <v>124938916</v>
       </c>
       <c r="B34" t="n">
-        <v>91950</v>
+        <v>56722</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4608,31 +4626,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4641,13 +4655,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446236</v>
+        <v>446512</v>
       </c>
       <c r="R34" t="n">
-        <v>7023806</v>
+        <v>7023807</v>
       </c>
       <c r="S34" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4676,7 +4690,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4686,7 +4700,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4713,10 +4727,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124938398</v>
+        <v>124939161</v>
       </c>
       <c r="B35" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4725,25 +4739,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4753,12 +4767,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4767,13 +4776,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446403</v>
+        <v>446288</v>
       </c>
       <c r="R35" t="n">
-        <v>7023878</v>
+        <v>7023859</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4802,7 +4811,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4812,12 +4821,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4844,10 +4853,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124937775</v>
+        <v>124936862</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4856,47 +4865,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446465</v>
+        <v>446512</v>
       </c>
       <c r="R36" t="n">
-        <v>7023899</v>
+        <v>7023771</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124940281</v>
+        <v>124937870</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,41 +818,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446268</v>
+        <v>446461</v>
       </c>
       <c r="R3" t="n">
-        <v>7023890</v>
+        <v>7023883</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +905,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1049,10 +1063,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124937870</v>
+        <v>124940281</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,55 +1075,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446461</v>
+        <v>446268</v>
       </c>
       <c r="R5" t="n">
-        <v>7023883</v>
+        <v>7023890</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1783,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124940379</v>
+        <v>124937238</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,52 +1795,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446275</v>
+        <v>446500</v>
       </c>
       <c r="R11" t="n">
-        <v>7023902</v>
+        <v>7023860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1872,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1882,12 +1868,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1907,17 +1893,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937238</v>
+        <v>124940379</v>
       </c>
       <c r="B12" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1926,38 +1912,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446500</v>
+        <v>446275</v>
       </c>
       <c r="R12" t="n">
-        <v>7023860</v>
+        <v>7023902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124937577</v>
+        <v>124939540</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,55 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446475</v>
+        <v>446196</v>
       </c>
       <c r="R2" t="n">
-        <v>7023891</v>
+        <v>7023833</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,17 +785,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124937870</v>
+        <v>124939161</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,40 +804,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -860,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446461</v>
+        <v>446288</v>
       </c>
       <c r="R3" t="n">
-        <v>7023883</v>
+        <v>7023859</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124940534</v>
+        <v>124939030</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -972,7 +953,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,13 +972,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446314</v>
+        <v>446512</v>
       </c>
       <c r="R4" t="n">
-        <v>7023930</v>
+        <v>7023807</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124940281</v>
+        <v>124940176</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,41 +1056,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446268</v>
+        <v>446236</v>
       </c>
       <c r="R5" t="n">
-        <v>7023890</v>
+        <v>7023806</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,12 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,22 +1144,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124939565</v>
+        <v>124938398</v>
       </c>
       <c r="B6" t="n">
-        <v>91700</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1196,34 +1172,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446214</v>
+        <v>446403</v>
       </c>
       <c r="R6" t="n">
-        <v>7023841</v>
+        <v>7023878</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,12 +1255,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124936198</v>
+        <v>124938507</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>91950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,25 +1299,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446431</v>
+        <v>446376</v>
       </c>
       <c r="R7" t="n">
-        <v>7023787</v>
+        <v>7023866</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1372,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124938918</v>
+        <v>124937346</v>
       </c>
       <c r="B8" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,41 +1416,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446330</v>
+        <v>446466</v>
       </c>
       <c r="R8" t="n">
-        <v>7023872</v>
+        <v>7023868</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,7 +1488,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,12 +1498,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,12 +1513,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1662,10 +1656,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124940260</v>
+        <v>124939729</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>98122</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1674,25 +1668,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1700,24 +1694,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446210</v>
+        <v>446196</v>
       </c>
       <c r="R10" t="n">
-        <v>7023879</v>
+        <v>7023847</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1746,7 +1745,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,7 +1755,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,19 +1775,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937238</v>
+        <v>124936198</v>
       </c>
       <c r="B11" t="n">
         <v>74901</v>
@@ -1823,10 +1827,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446500</v>
+        <v>446431</v>
       </c>
       <c r="R11" t="n">
-        <v>7023860</v>
+        <v>7023787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1858,7 +1862,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1872,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,7 +1904,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124940379</v>
+        <v>124937775</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1935,7 +1939,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1943,21 +1947,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446275</v>
+        <v>446465</v>
       </c>
       <c r="R12" t="n">
-        <v>7023902</v>
+        <v>7023899</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1989,7 +1988,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1999,12 +1998,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,17 +2023,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124939030</v>
+        <v>124938918</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>95335</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2043,52 +2042,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446512</v>
+        <v>446330</v>
       </c>
       <c r="R13" t="n">
-        <v>7023807</v>
+        <v>7023872</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2120,7 +2105,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2130,7 +2115,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2145,22 +2135,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124938507</v>
+        <v>124939668</v>
       </c>
       <c r="B14" t="n">
-        <v>91950</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2169,25 +2159,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2197,10 +2187,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446376</v>
+        <v>446191</v>
       </c>
       <c r="R14" t="n">
-        <v>7023866</v>
+        <v>7023833</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2232,7 +2222,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2242,12 +2232,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2274,10 +2264,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124936055</v>
+        <v>124936862</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2286,55 +2276,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446414</v>
+        <v>446512</v>
       </c>
       <c r="R15" t="n">
-        <v>7023792</v>
+        <v>7023771</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2363,7 +2339,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2373,12 +2349,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2398,17 +2374,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124935467</v>
+        <v>124938916</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2417,35 +2393,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2454,13 +2426,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446385</v>
+        <v>446512</v>
       </c>
       <c r="R16" t="n">
-        <v>7023868</v>
+        <v>7023807</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2489,7 +2461,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2499,7 +2471,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2519,17 +2491,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124937179</v>
+        <v>124939368</v>
       </c>
       <c r="B17" t="n">
-        <v>77743</v>
+        <v>91950</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2538,41 +2510,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446500</v>
+        <v>446236</v>
       </c>
       <c r="R17" t="n">
-        <v>7023860</v>
+        <v>7023806</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2601,7 +2582,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2611,12 +2592,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2631,22 +2607,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124939729</v>
+        <v>124937238</v>
       </c>
       <c r="B18" t="n">
-        <v>98122</v>
+        <v>74901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2655,52 +2631,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446196</v>
+        <v>446500</v>
       </c>
       <c r="R18" t="n">
-        <v>7023847</v>
+        <v>7023860</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2732,7 +2694,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2742,12 +2704,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2767,17 +2729,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124937224</v>
+        <v>124939441</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>95347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2786,25 +2748,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2814,13 +2776,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446500</v>
+        <v>446204</v>
       </c>
       <c r="R19" t="n">
-        <v>7023860</v>
+        <v>7023839</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2849,7 +2811,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2859,12 +2821,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2891,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124936685</v>
+        <v>124936055</v>
       </c>
       <c r="B20" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2903,41 +2865,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446500</v>
+        <v>446414</v>
       </c>
       <c r="R20" t="n">
-        <v>7023715</v>
+        <v>7023792</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2966,7 +2942,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2976,12 +2952,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3008,7 +2984,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124937355</v>
+        <v>124935467</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3043,7 +3019,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3051,21 +3027,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446493</v>
+        <v>446385</v>
       </c>
       <c r="R21" t="n">
-        <v>7023830</v>
+        <v>7023868</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3097,7 +3068,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3107,12 +3078,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3127,7 +3093,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3139,10 +3105,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124936966</v>
+        <v>124937224</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3151,52 +3117,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446533</v>
+        <v>446500</v>
       </c>
       <c r="R22" t="n">
-        <v>7023754</v>
+        <v>7023860</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3228,7 +3180,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3238,12 +3190,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>+ 1 vinterståndare</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3258,22 +3210,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124939441</v>
+        <v>124940281</v>
       </c>
       <c r="B23" t="n">
-        <v>95347</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3282,25 +3234,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3310,13 +3262,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446204</v>
+        <v>446268</v>
       </c>
       <c r="R23" t="n">
-        <v>7023839</v>
+        <v>7023890</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3345,7 +3297,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3355,12 +3307,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3387,10 +3339,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124937775</v>
+        <v>124936685</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3399,47 +3351,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446465</v>
+        <v>446500</v>
       </c>
       <c r="R24" t="n">
-        <v>7023899</v>
+        <v>7023715</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3471,7 +3414,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3481,12 +3424,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3513,10 +3456,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124935567</v>
+        <v>124940260</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3525,55 +3468,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446418</v>
+        <v>446210</v>
       </c>
       <c r="R25" t="n">
-        <v>7023888</v>
+        <v>7023879</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3602,7 +3540,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3612,12 +3550,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3632,22 +3565,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124939368</v>
+        <v>124937577</v>
       </c>
       <c r="B26" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3656,50 +3589,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446236</v>
+        <v>446475</v>
       </c>
       <c r="R26" t="n">
-        <v>7023806</v>
+        <v>7023891</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3728,7 +3666,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3738,7 +3676,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3753,7 +3696,7 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3765,10 +3708,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124937619</v>
+        <v>124937032</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3781,43 +3724,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446452</v>
+        <v>446505</v>
       </c>
       <c r="R27" t="n">
-        <v>7023890</v>
+        <v>7023805</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3849,7 +3783,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3859,12 +3793,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3891,10 +3825,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124940176</v>
+        <v>124940379</v>
       </c>
       <c r="B28" t="n">
-        <v>79851</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3903,41 +3837,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446236</v>
+        <v>446275</v>
       </c>
       <c r="R28" t="n">
-        <v>7023806</v>
+        <v>7023902</v>
       </c>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3966,7 +3914,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3976,7 +3924,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3991,22 +3944,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124938548</v>
+        <v>124936966</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4015,35 +3968,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4052,13 +4010,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446512</v>
+        <v>446533</v>
       </c>
       <c r="R29" t="n">
-        <v>7023807</v>
+        <v>7023754</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4087,7 +4045,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4097,7 +4055,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4124,10 +4087,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124937032</v>
+        <v>124937870</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4136,38 +4099,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446505</v>
+        <v>446461</v>
       </c>
       <c r="R30" t="n">
-        <v>7023805</v>
+        <v>7023883</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4199,7 +4176,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4209,12 +4186,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4234,17 +4211,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124939668</v>
+        <v>124937179</v>
       </c>
       <c r="B31" t="n">
-        <v>91008</v>
+        <v>77743</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4257,21 +4234,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4281,10 +4258,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446191</v>
+        <v>446500</v>
       </c>
       <c r="R31" t="n">
-        <v>7023833</v>
+        <v>7023860</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4316,7 +4293,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4326,12 +4303,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4358,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124937346</v>
+        <v>124937619</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -4393,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4403,17 +4380,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446466</v>
+        <v>446452</v>
       </c>
       <c r="R32" t="n">
-        <v>7023868</v>
+        <v>7023890</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4442,7 +4419,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4452,7 +4429,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4467,7 +4449,7 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -4479,10 +4461,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124938398</v>
+        <v>124938548</v>
       </c>
       <c r="B33" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4495,21 +4477,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4517,29 +4499,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446403</v>
+        <v>446512</v>
       </c>
       <c r="R33" t="n">
-        <v>7023878</v>
+        <v>7023807</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4568,7 +4545,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4578,12 +4555,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4598,22 +4570,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124938916</v>
+        <v>124940534</v>
       </c>
       <c r="B34" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4622,31 +4594,40 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4655,13 +4636,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446512</v>
+        <v>446314</v>
       </c>
       <c r="R34" t="n">
-        <v>7023807</v>
+        <v>7023930</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4690,7 +4671,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4700,7 +4681,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4727,10 +4708,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124939161</v>
+        <v>124935567</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4739,35 +4720,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4776,13 +4762,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446288</v>
+        <v>446418</v>
       </c>
       <c r="R35" t="n">
-        <v>7023859</v>
+        <v>7023888</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4811,7 +4797,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4821,12 +4807,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4853,10 +4839,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124936862</v>
+        <v>124939565</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91700</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4865,25 +4851,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4893,10 +4879,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446512</v>
+        <v>446214</v>
       </c>
       <c r="R36" t="n">
-        <v>7023771</v>
+        <v>7023841</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4928,7 +4914,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4938,12 +4924,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4963,17 +4949,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124939540</v>
+        <v>124937355</v>
       </c>
       <c r="B37" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4982,38 +4968,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446196</v>
+        <v>446493</v>
       </c>
       <c r="R37" t="n">
-        <v>7023833</v>
+        <v>7023830</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124939540</v>
+        <v>124936055</v>
       </c>
       <c r="B2" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446196</v>
+        <v>446414</v>
       </c>
       <c r="R2" t="n">
-        <v>7023833</v>
+        <v>7023792</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,17 +799,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124939161</v>
+        <v>124938548</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +818,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,24 +844,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446288</v>
+        <v>446512</v>
       </c>
       <c r="R3" t="n">
-        <v>7023859</v>
+        <v>7023807</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +915,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124939030</v>
+        <v>124937224</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,52 +939,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446512</v>
+        <v>446500</v>
       </c>
       <c r="R4" t="n">
-        <v>7023807</v>
+        <v>7023860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,22 +1032,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124940176</v>
+        <v>124939441</v>
       </c>
       <c r="B5" t="n">
-        <v>79851</v>
+        <v>95347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,37 +1060,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446236</v>
+        <v>446204</v>
       </c>
       <c r="R5" t="n">
-        <v>7023806</v>
+        <v>7023839</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,22 +1149,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124938398</v>
+        <v>124940379</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,30 +1173,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446403</v>
+        <v>446275</v>
       </c>
       <c r="R6" t="n">
-        <v>7023878</v>
+        <v>7023902</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,12 +1260,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,17 +1285,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124938507</v>
+        <v>124937577</v>
       </c>
       <c r="B7" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,41 +1304,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446376</v>
+        <v>446475</v>
       </c>
       <c r="R7" t="n">
-        <v>7023866</v>
+        <v>7023891</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,7 +1381,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,12 +1391,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,10 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937346</v>
+        <v>124938918</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,50 +1435,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446466</v>
+        <v>446330</v>
       </c>
       <c r="R8" t="n">
-        <v>7023868</v>
+        <v>7023872</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1488,7 +1498,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1498,7 +1508,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,22 +1528,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124936204</v>
+        <v>124938916</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,40 +1552,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1579,13 +1585,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446448</v>
+        <v>446512</v>
       </c>
       <c r="R9" t="n">
-        <v>7023801</v>
+        <v>7023807</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1614,7 +1620,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,12 +1630,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939729</v>
+        <v>124937619</v>
       </c>
       <c r="B10" t="n">
-        <v>98122</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1668,40 +1669,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1710,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446196</v>
+        <v>446452</v>
       </c>
       <c r="R10" t="n">
-        <v>7023847</v>
+        <v>7023890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1745,7 +1741,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1755,12 +1751,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1787,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124936198</v>
+        <v>124938398</v>
       </c>
       <c r="B11" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1799,38 +1795,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446431</v>
+        <v>446403</v>
       </c>
       <c r="R11" t="n">
-        <v>7023787</v>
+        <v>7023878</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,7 +1872,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1872,12 +1882,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,10 +1914,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937775</v>
+        <v>124940260</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1916,50 +1926,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446465</v>
+        <v>446210</v>
       </c>
       <c r="R12" t="n">
-        <v>7023899</v>
+        <v>7023879</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1988,7 +1998,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1998,12 +2008,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,22 +2023,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124938918</v>
+        <v>124936198</v>
       </c>
       <c r="B13" t="n">
-        <v>95335</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2042,25 +2047,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2070,10 +2075,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446330</v>
+        <v>446431</v>
       </c>
       <c r="R13" t="n">
-        <v>7023872</v>
+        <v>7023787</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2105,7 +2110,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2115,12 +2120,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2147,10 +2152,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124939668</v>
+        <v>124940534</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2159,41 +2164,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R14" t="n">
-        <v>7023833</v>
+        <v>7023930</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2222,7 +2241,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2232,12 +2251,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2252,22 +2266,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124936862</v>
+        <v>124937355</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2276,38 +2290,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446512</v>
+        <v>446493</v>
       </c>
       <c r="R15" t="n">
-        <v>7023771</v>
+        <v>7023830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2339,7 +2367,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2349,12 +2377,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2374,17 +2402,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124938916</v>
+        <v>124936685</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>91950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2397,42 +2425,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446512</v>
+        <v>446500</v>
       </c>
       <c r="R16" t="n">
-        <v>7023807</v>
+        <v>7023715</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2461,7 +2484,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2471,7 +2494,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2486,22 +2514,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124939368</v>
+        <v>124936204</v>
       </c>
       <c r="B17" t="n">
-        <v>91950</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2510,30 +2538,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2541,19 +2569,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446236</v>
+        <v>446448</v>
       </c>
       <c r="R17" t="n">
-        <v>7023806</v>
+        <v>7023801</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2582,7 +2615,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2592,7 +2625,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2619,10 +2657,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124937238</v>
+        <v>124935467</v>
       </c>
       <c r="B18" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2631,38 +2669,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446500</v>
+        <v>446385</v>
       </c>
       <c r="R18" t="n">
-        <v>7023860</v>
+        <v>7023868</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2694,7 +2741,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2704,12 +2751,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2724,7 +2766,7 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2736,10 +2778,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124939441</v>
+        <v>124939030</v>
       </c>
       <c r="B19" t="n">
-        <v>95347</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2748,41 +2790,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446204</v>
+        <v>446512</v>
       </c>
       <c r="R19" t="n">
-        <v>7023839</v>
+        <v>7023807</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2811,7 +2867,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2821,12 +2877,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På marken i fuktig granskog</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2841,22 +2892,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124936055</v>
+        <v>124936862</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,55 +2916,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446414</v>
+        <v>446512</v>
       </c>
       <c r="R20" t="n">
-        <v>7023792</v>
+        <v>7023771</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2942,7 +2979,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2952,12 +2989,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2984,10 +3021,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124935467</v>
+        <v>124938507</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2996,47 +3033,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446385</v>
+        <v>446376</v>
       </c>
       <c r="R21" t="n">
-        <v>7023868</v>
+        <v>7023866</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3068,7 +3096,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3078,7 +3106,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3093,7 +3126,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3105,10 +3138,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124937224</v>
+        <v>124937179</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3121,21 +3154,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3195,7 +3228,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3215,7 +3248,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3339,10 +3372,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124936685</v>
+        <v>124937775</v>
       </c>
       <c r="B24" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3351,38 +3384,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446500</v>
+        <v>446465</v>
       </c>
       <c r="R24" t="n">
-        <v>7023715</v>
+        <v>7023899</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3414,7 +3456,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3424,12 +3466,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3456,10 +3498,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124940260</v>
+        <v>124937032</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3472,46 +3514,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446210</v>
+        <v>446505</v>
       </c>
       <c r="R25" t="n">
-        <v>7023879</v>
+        <v>7023805</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3540,7 +3573,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3550,7 +3583,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,22 +3603,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124937577</v>
+        <v>124939161</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3589,40 +3627,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3631,10 +3664,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446475</v>
+        <v>446288</v>
       </c>
       <c r="R26" t="n">
-        <v>7023891</v>
+        <v>7023859</v>
       </c>
       <c r="S26" t="n">
         <v>7</v>
@@ -3666,7 +3699,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3676,12 +3709,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3708,10 +3741,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124937032</v>
+        <v>124937870</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3720,38 +3753,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446505</v>
+        <v>446461</v>
       </c>
       <c r="R27" t="n">
-        <v>7023805</v>
+        <v>7023883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3783,7 +3830,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3793,12 +3840,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3825,10 +3872,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124940379</v>
+        <v>124939540</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3837,52 +3884,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446275</v>
+        <v>446196</v>
       </c>
       <c r="R28" t="n">
-        <v>7023902</v>
+        <v>7023833</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3914,7 +3947,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3924,12 +3957,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3949,17 +3982,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124936966</v>
+        <v>124940176</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>79851</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3968,55 +4001,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446533</v>
+        <v>446236</v>
       </c>
       <c r="R29" t="n">
-        <v>7023754</v>
+        <v>7023806</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4045,7 +4064,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4055,12 +4074,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:34</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>+ 1 vinterståndare</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4087,10 +4101,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124937870</v>
+        <v>124937346</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4099,55 +4113,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446461</v>
+        <v>446466</v>
       </c>
       <c r="R30" t="n">
-        <v>7023883</v>
+        <v>7023868</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4176,7 +4185,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4186,12 +4195,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4206,22 +4210,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124937179</v>
+        <v>124937238</v>
       </c>
       <c r="B31" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4234,21 +4238,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4293,7 +4297,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4303,12 +4307,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,10 +4339,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124937619</v>
+        <v>124939668</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4351,43 +4355,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446452</v>
+        <v>446191</v>
       </c>
       <c r="R32" t="n">
-        <v>7023890</v>
+        <v>7023833</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4414,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4429,12 +4424,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4454,17 +4449,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124938548</v>
+        <v>124939565</v>
       </c>
       <c r="B33" t="n">
-        <v>57883</v>
+        <v>91700</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4477,46 +4472,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446512</v>
+        <v>446214</v>
       </c>
       <c r="R33" t="n">
-        <v>7023807</v>
+        <v>7023841</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4545,7 +4531,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4555,7 +4541,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4570,22 +4561,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124940534</v>
+        <v>124939368</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4594,40 +4585,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4636,13 +4622,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446314</v>
+        <v>446236</v>
       </c>
       <c r="R34" t="n">
-        <v>7023930</v>
+        <v>7023806</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4671,7 +4657,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4681,7 +4667,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4708,7 +4694,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124935567</v>
+        <v>124936966</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4743,7 +4729,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4758,17 +4744,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446418</v>
+        <v>446533</v>
       </c>
       <c r="R35" t="n">
-        <v>7023888</v>
+        <v>7023754</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4797,7 +4783,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4807,12 +4793,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4827,22 +4813,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124939565</v>
+        <v>124935567</v>
       </c>
       <c r="B36" t="n">
-        <v>91700</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4851,41 +4837,55 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446214</v>
+        <v>446418</v>
       </c>
       <c r="R36" t="n">
-        <v>7023841</v>
+        <v>7023888</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4949,17 +4949,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124937355</v>
+        <v>124939729</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4968,30 +4968,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446493</v>
+        <v>446196</v>
       </c>
       <c r="R37" t="n">
-        <v>7023830</v>
+        <v>7023847</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124936055</v>
+        <v>124938548</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,55 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446414</v>
+        <v>446512</v>
       </c>
       <c r="R2" t="n">
-        <v>7023792</v>
+        <v>7023807</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124938548</v>
+        <v>124936055</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,50 +808,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446512</v>
+        <v>446414</v>
       </c>
       <c r="R3" t="n">
-        <v>7023807</v>
+        <v>7023792</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,12 +915,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124940534</v>
+        <v>124936685</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,55 +2164,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446314</v>
+        <v>446500</v>
       </c>
       <c r="R14" t="n">
-        <v>7023930</v>
+        <v>7023715</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2241,7 +2227,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2251,7 +2237,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,19 +2257,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124937355</v>
+        <v>124940534</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2313,7 +2304,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2328,17 +2319,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446493</v>
+        <v>446314</v>
       </c>
       <c r="R15" t="n">
-        <v>7023830</v>
+        <v>7023930</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2358,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2377,12 +2368,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2397,22 +2383,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124936685</v>
+        <v>124937355</v>
       </c>
       <c r="B16" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2421,38 +2407,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446500</v>
+        <v>446493</v>
       </c>
       <c r="R16" t="n">
-        <v>7023715</v>
+        <v>7023830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3255,10 +3255,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124940281</v>
+        <v>124937775</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3267,41 +3267,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446268</v>
+        <v>446465</v>
       </c>
       <c r="R23" t="n">
-        <v>7023890</v>
+        <v>7023899</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3330,7 +3339,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3340,12 +3349,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3372,10 +3381,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124937775</v>
+        <v>124940281</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3384,50 +3393,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446465</v>
+        <v>446268</v>
       </c>
       <c r="R24" t="n">
-        <v>7023899</v>
+        <v>7023890</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4573,10 +4573,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124939368</v>
+        <v>124936966</v>
       </c>
       <c r="B34" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4585,35 +4585,40 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4622,13 +4627,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446236</v>
+        <v>446533</v>
       </c>
       <c r="R34" t="n">
-        <v>7023806</v>
+        <v>7023754</v>
       </c>
       <c r="S34" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4657,7 +4662,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4667,7 +4672,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4694,7 +4704,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124936966</v>
+        <v>124935567</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4729,7 +4739,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4744,17 +4754,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446533</v>
+        <v>446418</v>
       </c>
       <c r="R35" t="n">
-        <v>7023754</v>
+        <v>7023888</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4783,7 +4793,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4793,12 +4803,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>+ 1 vinterståndare</t>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4813,22 +4823,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124935567</v>
+        <v>124939729</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4837,30 +4847,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4879,13 +4889,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446418</v>
+        <v>446196</v>
       </c>
       <c r="R36" t="n">
-        <v>7023888</v>
+        <v>7023847</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4914,7 +4924,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4924,12 +4934,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4956,10 +4966,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124939729</v>
+        <v>124939368</v>
       </c>
       <c r="B37" t="n">
-        <v>98122</v>
+        <v>91950</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4972,51 +4982,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446196</v>
+        <v>446236</v>
       </c>
       <c r="R37" t="n">
-        <v>7023847</v>
+        <v>7023806</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5045,7 +5050,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +5060,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5075,12 +5075,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937577</v>
+        <v>124938918</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>95335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,55 +1304,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446475</v>
+        <v>446330</v>
       </c>
       <c r="R7" t="n">
-        <v>7023891</v>
+        <v>7023872</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1381,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1391,12 +1377,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124938918</v>
+        <v>124938916</v>
       </c>
       <c r="B8" t="n">
-        <v>95335</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1439,37 +1425,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446330</v>
+        <v>446512</v>
       </c>
       <c r="R8" t="n">
-        <v>7023872</v>
+        <v>7023807</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,11 +1500,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,22 +1514,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124938916</v>
+        <v>124937577</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,46 +1538,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446512</v>
+        <v>446475</v>
       </c>
       <c r="R9" t="n">
-        <v>7023807</v>
+        <v>7023891</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,7 +1615,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1630,7 +1625,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,12 +1645,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3255,10 +3255,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124937775</v>
+        <v>124940281</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3267,50 +3267,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446465</v>
+        <v>446268</v>
       </c>
       <c r="R23" t="n">
-        <v>7023899</v>
+        <v>7023890</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3339,7 +3330,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3349,12 +3340,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3381,10 +3372,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124940281</v>
+        <v>124937775</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3393,41 +3384,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446268</v>
+        <v>446465</v>
       </c>
       <c r="R24" t="n">
-        <v>7023890</v>
+        <v>7023899</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124938548</v>
+        <v>124935467</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446512</v>
+        <v>446385</v>
       </c>
       <c r="R2" t="n">
-        <v>7023807</v>
+        <v>7023868</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124936055</v>
+        <v>124936966</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446414</v>
+        <v>446533</v>
       </c>
       <c r="R3" t="n">
-        <v>7023792</v>
+        <v>7023754</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,22 +915,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124937224</v>
+        <v>124940379</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,38 +939,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446500</v>
+        <v>446275</v>
       </c>
       <c r="R4" t="n">
-        <v>7023860</v>
+        <v>7023902</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +1026,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,17 +1051,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124939441</v>
+        <v>124937224</v>
       </c>
       <c r="B5" t="n">
-        <v>95347</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,13 +1098,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446204</v>
+        <v>446500</v>
       </c>
       <c r="R5" t="n">
-        <v>7023839</v>
+        <v>7023860</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1133,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1143,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124940379</v>
+        <v>124936685</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,52 +1187,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446275</v>
+        <v>446500</v>
       </c>
       <c r="R6" t="n">
-        <v>7023902</v>
+        <v>7023715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124938918</v>
+        <v>124940260</v>
       </c>
       <c r="B7" t="n">
-        <v>95335</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,41 +1304,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446330</v>
+        <v>446210</v>
       </c>
       <c r="R7" t="n">
-        <v>7023872</v>
+        <v>7023879</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,12 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,22 +1401,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124938916</v>
+        <v>124936862</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,46 +1425,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>446512</v>
       </c>
       <c r="R8" t="n">
-        <v>7023807</v>
+        <v>7023771</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,7 +1488,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,7 +1498,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,22 +1518,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937577</v>
+        <v>124938916</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,55 +1542,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446475</v>
+        <v>446512</v>
       </c>
       <c r="R9" t="n">
-        <v>7023891</v>
+        <v>7023807</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1625,12 +1620,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,22 +1635,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937619</v>
+        <v>124936198</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,43 +1663,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446452</v>
+        <v>446431</v>
       </c>
       <c r="R10" t="n">
-        <v>7023890</v>
+        <v>7023787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1741,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1751,12 +1732,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,17 +1757,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124938398</v>
+        <v>124938548</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1799,21 +1780,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1821,29 +1802,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446403</v>
+        <v>446512</v>
       </c>
       <c r="R11" t="n">
-        <v>7023878</v>
+        <v>7023807</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1872,7 +1848,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1882,12 +1858,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,7 +1873,7 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -1914,10 +1885,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124940260</v>
+        <v>124937577</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1926,50 +1897,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446210</v>
+        <v>446475</v>
       </c>
       <c r="R12" t="n">
-        <v>7023879</v>
+        <v>7023891</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1998,7 +1974,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2008,7 +1984,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,22 +2004,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124936198</v>
+        <v>124939729</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>98122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2047,38 +2028,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446431</v>
+        <v>446196</v>
       </c>
       <c r="R13" t="n">
-        <v>7023787</v>
+        <v>7023847</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2110,7 +2105,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2120,12 +2115,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2152,10 +2147,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124936685</v>
+        <v>124936055</v>
       </c>
       <c r="B14" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,41 +2159,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446500</v>
+        <v>446414</v>
       </c>
       <c r="R14" t="n">
-        <v>7023715</v>
+        <v>7023792</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2227,7 +2236,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2237,12 +2246,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2269,10 +2278,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124940534</v>
+        <v>124937238</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2281,55 +2290,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446314</v>
+        <v>446500</v>
       </c>
       <c r="R15" t="n">
-        <v>7023930</v>
+        <v>7023860</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2358,7 +2353,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2368,7 +2363,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2383,22 +2383,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124937355</v>
+        <v>124937032</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2407,52 +2407,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446493</v>
+        <v>446505</v>
       </c>
       <c r="R16" t="n">
-        <v>7023830</v>
+        <v>7023805</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2484,7 +2470,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2494,12 +2480,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2526,10 +2512,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124936204</v>
+        <v>124937870</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2538,55 +2524,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446448</v>
+        <v>446461</v>
       </c>
       <c r="R17" t="n">
-        <v>7023801</v>
+        <v>7023883</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2615,7 +2601,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2625,12 +2611,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,19 +2631,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124935467</v>
+        <v>124937355</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2692,7 +2678,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2700,16 +2686,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446385</v>
+        <v>446493</v>
       </c>
       <c r="R18" t="n">
-        <v>7023868</v>
+        <v>7023830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2741,7 +2732,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2751,7 +2742,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2766,22 +2762,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124939030</v>
+        <v>124939441</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>95347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2790,55 +2786,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446512</v>
+        <v>446204</v>
       </c>
       <c r="R19" t="n">
-        <v>7023807</v>
+        <v>7023839</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2867,7 +2849,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2877,7 +2859,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2892,22 +2879,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124936862</v>
+        <v>124935567</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2916,41 +2903,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446512</v>
+        <v>446418</v>
       </c>
       <c r="R20" t="n">
-        <v>7023771</v>
+        <v>7023888</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2979,7 +2980,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2989,12 +2990,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3021,10 +3022,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124938507</v>
+        <v>124939565</v>
       </c>
       <c r="B21" t="n">
-        <v>91950</v>
+        <v>91700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3037,21 +3038,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3061,10 +3062,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446376</v>
+        <v>446214</v>
       </c>
       <c r="R21" t="n">
-        <v>7023866</v>
+        <v>7023841</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3096,7 +3097,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3106,12 +3107,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3131,17 +3132,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124937179</v>
+        <v>124936204</v>
       </c>
       <c r="B22" t="n">
-        <v>77743</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3154,37 +3155,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446500</v>
+        <v>446448</v>
       </c>
       <c r="R22" t="n">
-        <v>7023860</v>
+        <v>7023801</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3213,7 +3228,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3223,12 +3238,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3243,7 +3258,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3255,10 +3270,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124940281</v>
+        <v>124939540</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>105102</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3267,25 +3282,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3295,13 +3310,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446268</v>
+        <v>446196</v>
       </c>
       <c r="R23" t="n">
-        <v>7023890</v>
+        <v>7023833</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3330,7 +3345,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3340,12 +3355,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3365,14 +3380,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124937775</v>
+        <v>124939030</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3407,7 +3422,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3415,16 +3430,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446465</v>
+        <v>446512</v>
       </c>
       <c r="R24" t="n">
-        <v>7023899</v>
+        <v>7023807</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3456,7 +3476,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3466,12 +3486,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3486,22 +3501,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124937032</v>
+        <v>124939668</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3514,21 +3529,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3538,10 +3553,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446505</v>
+        <v>446191</v>
       </c>
       <c r="R25" t="n">
-        <v>7023805</v>
+        <v>7023833</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3573,7 +3588,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3583,12 +3598,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3615,7 +3630,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124939161</v>
+        <v>124937619</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3650,7 +3665,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3664,13 +3679,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446288</v>
+        <v>446452</v>
       </c>
       <c r="R26" t="n">
-        <v>7023859</v>
+        <v>7023890</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3699,7 +3714,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3709,12 +3724,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3741,10 +3756,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124937870</v>
+        <v>124938507</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3753,52 +3768,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446461</v>
+        <v>446376</v>
       </c>
       <c r="R27" t="n">
-        <v>7023883</v>
+        <v>7023866</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3830,7 +3831,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3840,12 +3841,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3865,17 +3866,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124939540</v>
+        <v>124939161</v>
       </c>
       <c r="B28" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3884,41 +3885,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446196</v>
+        <v>446288</v>
       </c>
       <c r="R28" t="n">
-        <v>7023833</v>
+        <v>7023859</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3947,7 +3957,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3957,12 +3967,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3989,10 +3999,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124940176</v>
+        <v>124940281</v>
       </c>
       <c r="B29" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4001,41 +4011,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446236</v>
+        <v>446268</v>
       </c>
       <c r="R29" t="n">
-        <v>7023806</v>
+        <v>7023890</v>
       </c>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4064,7 +4074,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4074,7 +4084,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4089,22 +4104,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124937346</v>
+        <v>124938398</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4113,50 +4128,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446466</v>
+        <v>446403</v>
       </c>
       <c r="R30" t="n">
-        <v>7023868</v>
+        <v>7023878</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4185,7 +4205,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4195,7 +4215,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4210,22 +4235,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124937238</v>
+        <v>124937346</v>
       </c>
       <c r="B31" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4238,37 +4263,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446500</v>
+        <v>446466</v>
       </c>
       <c r="R31" t="n">
-        <v>7023860</v>
+        <v>7023868</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4297,7 +4331,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4307,12 +4341,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4327,22 +4356,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124939668</v>
+        <v>124940176</v>
       </c>
       <c r="B32" t="n">
-        <v>91008</v>
+        <v>79851</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4351,41 +4380,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446191</v>
+        <v>446236</v>
       </c>
       <c r="R32" t="n">
-        <v>7023833</v>
+        <v>7023806</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4414,7 +4443,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4424,12 +4453,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4444,22 +4468,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124939565</v>
+        <v>124939368</v>
       </c>
       <c r="B33" t="n">
-        <v>91700</v>
+        <v>91950</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4472,37 +4496,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446214</v>
+        <v>446236</v>
       </c>
       <c r="R33" t="n">
-        <v>7023841</v>
+        <v>7023806</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4531,7 +4564,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4541,12 +4574,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4561,22 +4589,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124936966</v>
+        <v>124938918</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>95335</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4585,52 +4613,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446533</v>
+        <v>446330</v>
       </c>
       <c r="R34" t="n">
-        <v>7023754</v>
+        <v>7023872</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4662,7 +4676,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4672,12 +4686,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>+ 1 vinterståndare</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4692,19 +4706,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124935567</v>
+        <v>124937775</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4739,7 +4753,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4747,24 +4761,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446418</v>
+        <v>446465</v>
       </c>
       <c r="R35" t="n">
-        <v>7023888</v>
+        <v>7023899</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4793,7 +4802,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4803,12 +4812,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4835,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124939729</v>
+        <v>124940534</v>
       </c>
       <c r="B36" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4847,30 +4856,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4885,17 +4894,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446196</v>
+        <v>446314</v>
       </c>
       <c r="R36" t="n">
-        <v>7023847</v>
+        <v>7023930</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4924,7 +4933,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4934,12 +4943,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4954,22 +4958,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124939368</v>
+        <v>124937179</v>
       </c>
       <c r="B37" t="n">
-        <v>91950</v>
+        <v>77743</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4978,50 +4982,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446236</v>
+        <v>446500</v>
       </c>
       <c r="R37" t="n">
-        <v>7023806</v>
+        <v>7023860</v>
       </c>
       <c r="S37" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5050,7 +5045,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5060,7 +5055,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5075,12 +5075,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124935467</v>
+        <v>124939540</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446385</v>
+        <v>446196</v>
       </c>
       <c r="R2" t="n">
-        <v>7023868</v>
+        <v>7023833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124936966</v>
+        <v>124940281</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,55 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446533</v>
+        <v>446268</v>
       </c>
       <c r="R3" t="n">
-        <v>7023754</v>
+        <v>7023890</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>+ 1 vinterståndare</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124940379</v>
+        <v>124936055</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -962,7 +944,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -981,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446275</v>
+        <v>446414</v>
       </c>
       <c r="R4" t="n">
-        <v>7023902</v>
+        <v>7023792</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,17 +1033,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124937224</v>
+        <v>124938918</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1052,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1098,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446500</v>
+        <v>446330</v>
       </c>
       <c r="R5" t="n">
-        <v>7023860</v>
+        <v>7023872</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1143,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124936685</v>
+        <v>124938548</v>
       </c>
       <c r="B6" t="n">
-        <v>91950</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,37 +1173,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446500</v>
+        <v>446512</v>
       </c>
       <c r="R6" t="n">
-        <v>7023715</v>
+        <v>7023807</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,12 +1251,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,22 +1266,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124940260</v>
+        <v>124940534</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,50 +1290,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446210</v>
+        <v>446314</v>
       </c>
       <c r="R7" t="n">
-        <v>7023879</v>
+        <v>7023930</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124936862</v>
+        <v>124938507</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,25 +1416,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1453,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446512</v>
+        <v>446376</v>
       </c>
       <c r="R8" t="n">
-        <v>7023771</v>
+        <v>7023866</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1498,12 +1489,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124938916</v>
+        <v>124938398</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,42 +1537,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446512</v>
+        <v>446403</v>
       </c>
       <c r="R9" t="n">
-        <v>7023807</v>
+        <v>7023878</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,7 +1620,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1640,7 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1647,10 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124936198</v>
+        <v>124937346</v>
       </c>
       <c r="B10" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1663,37 +1668,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446431</v>
+        <v>446466</v>
       </c>
       <c r="R10" t="n">
-        <v>7023787</v>
+        <v>7023868</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,12 +1746,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,7 +1761,7 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1764,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124938548</v>
+        <v>124937032</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,50 +1785,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446512</v>
+        <v>446505</v>
       </c>
       <c r="R11" t="n">
-        <v>7023807</v>
+        <v>7023805</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1858,7 +1858,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,7 +1878,7 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -1885,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937577</v>
+        <v>124937238</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1897,55 +1902,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446475</v>
+        <v>446500</v>
       </c>
       <c r="R12" t="n">
-        <v>7023891</v>
+        <v>7023860</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1974,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1984,12 +1975,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,10 +2007,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124939729</v>
+        <v>124936862</v>
       </c>
       <c r="B13" t="n">
-        <v>98122</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,52 +2019,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446196</v>
+        <v>446512</v>
       </c>
       <c r="R13" t="n">
-        <v>7023847</v>
+        <v>7023771</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2105,7 +2082,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2115,12 +2092,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2147,10 +2124,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124936055</v>
+        <v>124937179</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2159,55 +2136,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446414</v>
+        <v>446500</v>
       </c>
       <c r="R14" t="n">
-        <v>7023792</v>
+        <v>7023860</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2236,7 +2199,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2246,12 +2209,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2278,10 +2241,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124937238</v>
+        <v>124935467</v>
       </c>
       <c r="B15" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2290,38 +2253,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446500</v>
+        <v>446385</v>
       </c>
       <c r="R15" t="n">
-        <v>7023860</v>
+        <v>7023868</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2353,7 +2325,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2363,12 +2335,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2383,22 +2350,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124937032</v>
+        <v>124937870</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2407,38 +2374,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446505</v>
+        <v>446461</v>
       </c>
       <c r="R16" t="n">
-        <v>7023805</v>
+        <v>7023883</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2470,7 +2451,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2480,12 +2461,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2512,10 +2493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124937870</v>
+        <v>124937224</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2524,52 +2505,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446461</v>
+        <v>446500</v>
       </c>
       <c r="R17" t="n">
-        <v>7023883</v>
+        <v>7023860</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2601,7 +2568,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2611,12 +2578,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2643,7 +2610,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124937355</v>
+        <v>124935567</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2678,7 +2645,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2697,13 +2664,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446493</v>
+        <v>446418</v>
       </c>
       <c r="R18" t="n">
-        <v>7023830</v>
+        <v>7023888</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2732,7 +2699,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2742,12 +2709,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2774,10 +2741,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124939441</v>
+        <v>124937577</v>
       </c>
       <c r="B19" t="n">
-        <v>95347</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2786,41 +2753,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446204</v>
+        <v>446475</v>
       </c>
       <c r="R19" t="n">
-        <v>7023839</v>
+        <v>7023891</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2849,7 +2830,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2859,12 +2840,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2891,10 +2872,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124935567</v>
+        <v>124939161</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2903,40 +2884,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2945,13 +2921,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446418</v>
+        <v>446288</v>
       </c>
       <c r="R20" t="n">
-        <v>7023888</v>
+        <v>7023859</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2980,7 +2956,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2990,12 +2966,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3022,10 +2998,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124939565</v>
+        <v>124939030</v>
       </c>
       <c r="B21" t="n">
-        <v>91700</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3034,38 +3010,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446214</v>
+        <v>446512</v>
       </c>
       <c r="R21" t="n">
-        <v>7023841</v>
+        <v>7023807</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3097,7 +3087,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3107,12 +3097,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3127,7 +3112,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3139,10 +3124,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124936204</v>
+        <v>124936198</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3155,51 +3140,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446448</v>
+        <v>446431</v>
       </c>
       <c r="R22" t="n">
-        <v>7023801</v>
+        <v>7023787</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3243,7 +3214,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3258,7 +3229,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3270,10 +3241,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124939540</v>
+        <v>124939565</v>
       </c>
       <c r="B23" t="n">
-        <v>105102</v>
+        <v>91700</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3286,21 +3257,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3310,10 +3281,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446196</v>
+        <v>446214</v>
       </c>
       <c r="R23" t="n">
-        <v>7023833</v>
+        <v>7023841</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3345,7 +3316,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3355,12 +3326,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3380,14 +3351,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124939030</v>
+        <v>124936966</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3422,7 +3393,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3441,10 +3412,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446512</v>
+        <v>446533</v>
       </c>
       <c r="R24" t="n">
-        <v>7023807</v>
+        <v>7023754</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3476,7 +3447,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3486,7 +3457,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3513,10 +3489,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124939668</v>
+        <v>124936204</v>
       </c>
       <c r="B25" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3529,37 +3505,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446191</v>
+        <v>446448</v>
       </c>
       <c r="R25" t="n">
-        <v>7023833</v>
+        <v>7023801</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3588,7 +3578,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3598,12 +3588,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3618,22 +3608,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124937619</v>
+        <v>124937775</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3642,35 +3632,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3679,10 +3669,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446452</v>
+        <v>446465</v>
       </c>
       <c r="R26" t="n">
-        <v>7023890</v>
+        <v>7023899</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3714,7 +3704,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3724,12 +3714,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3756,10 +3746,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124938507</v>
+        <v>124940379</v>
       </c>
       <c r="B27" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3768,38 +3758,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446376</v>
+        <v>446275</v>
       </c>
       <c r="R27" t="n">
-        <v>7023866</v>
+        <v>7023902</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3831,7 +3835,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3841,12 +3845,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3866,17 +3870,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124939161</v>
+        <v>124940260</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3889,21 +3893,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3911,24 +3915,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446288</v>
+        <v>446210</v>
       </c>
       <c r="R28" t="n">
-        <v>7023859</v>
+        <v>7023879</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3957,7 +3961,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3967,12 +3971,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3987,22 +3986,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124940281</v>
+        <v>124937355</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4011,41 +4010,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446268</v>
+        <v>446493</v>
       </c>
       <c r="R29" t="n">
-        <v>7023890</v>
+        <v>7023830</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4074,7 +4087,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4084,12 +4097,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4116,10 +4129,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124938398</v>
+        <v>124937619</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4128,40 +4141,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4170,10 +4178,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446403</v>
+        <v>446452</v>
       </c>
       <c r="R30" t="n">
-        <v>7023878</v>
+        <v>7023890</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4205,7 +4213,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4215,12 +4223,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4247,10 +4255,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124937346</v>
+        <v>124939368</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91950</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4259,35 +4267,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4296,13 +4304,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446466</v>
+        <v>446236</v>
       </c>
       <c r="R31" t="n">
-        <v>7023868</v>
+        <v>7023806</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4331,7 +4339,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4341,7 +4349,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4368,10 +4376,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124940176</v>
+        <v>124939441</v>
       </c>
       <c r="B32" t="n">
-        <v>79851</v>
+        <v>95347</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4384,37 +4392,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446236</v>
+        <v>446204</v>
       </c>
       <c r="R32" t="n">
-        <v>7023806</v>
+        <v>7023839</v>
       </c>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4443,7 +4451,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4453,7 +4461,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4468,22 +4481,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124939368</v>
+        <v>124939729</v>
       </c>
       <c r="B33" t="n">
-        <v>91950</v>
+        <v>98122</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4496,46 +4509,51 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446236</v>
+        <v>446196</v>
       </c>
       <c r="R33" t="n">
-        <v>7023806</v>
+        <v>7023847</v>
       </c>
       <c r="S33" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4564,7 +4582,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4574,7 +4592,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4589,22 +4612,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124938918</v>
+        <v>124938916</v>
       </c>
       <c r="B34" t="n">
-        <v>95335</v>
+        <v>56722</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4617,37 +4640,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2809</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446330</v>
+        <v>446512</v>
       </c>
       <c r="R34" t="n">
-        <v>7023872</v>
+        <v>7023807</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4687,11 +4715,6 @@
       <c r="AB34" t="inlineStr">
         <is>
           <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4706,22 +4729,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124937775</v>
+        <v>124939668</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>91008</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4730,47 +4753,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446465</v>
+        <v>446191</v>
       </c>
       <c r="R35" t="n">
-        <v>7023899</v>
+        <v>7023833</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4802,7 +4816,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4812,12 +4826,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4844,10 +4858,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124940534</v>
+        <v>124936685</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4856,55 +4870,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446314</v>
+        <v>446500</v>
       </c>
       <c r="R36" t="n">
-        <v>7023930</v>
+        <v>7023715</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4943,7 +4943,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4958,22 +4963,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124937179</v>
+        <v>124940176</v>
       </c>
       <c r="B37" t="n">
-        <v>77743</v>
+        <v>79851</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4982,41 +4987,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446500</v>
+        <v>446236</v>
       </c>
       <c r="R37" t="n">
-        <v>7023860</v>
+        <v>7023806</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5045,7 +5050,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +5060,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5075,12 +5075,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124939540</v>
+        <v>124938916</v>
       </c>
       <c r="B2" t="n">
-        <v>105102</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446196</v>
+        <v>446512</v>
       </c>
       <c r="R2" t="n">
-        <v>7023833</v>
+        <v>7023807</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124940281</v>
+        <v>124939030</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +804,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446268</v>
+        <v>446512</v>
       </c>
       <c r="R3" t="n">
-        <v>7023890</v>
+        <v>7023807</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,19 +906,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124936055</v>
+        <v>124935467</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -944,7 +953,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,24 +961,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446414</v>
+        <v>446385</v>
       </c>
       <c r="R4" t="n">
-        <v>7023792</v>
+        <v>7023868</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,22 +1027,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124938918</v>
+        <v>124939565</v>
       </c>
       <c r="B5" t="n">
-        <v>95335</v>
+        <v>91700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,21 +1055,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1080,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446330</v>
+        <v>446214</v>
       </c>
       <c r="R5" t="n">
-        <v>7023872</v>
+        <v>7023841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1124,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124938548</v>
+        <v>124937224</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,50 +1168,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446512</v>
+        <v>446500</v>
       </c>
       <c r="R6" t="n">
-        <v>7023807</v>
+        <v>7023860</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,7 +1241,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,22 +1261,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124940534</v>
+        <v>124937346</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,40 +1285,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1332,13 +1322,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446314</v>
+        <v>446466</v>
       </c>
       <c r="R7" t="n">
-        <v>7023930</v>
+        <v>7023868</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,7 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124938507</v>
+        <v>124939441</v>
       </c>
       <c r="B8" t="n">
-        <v>91950</v>
+        <v>95347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1420,21 +1410,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>2813</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1444,13 +1434,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446376</v>
+        <v>446204</v>
       </c>
       <c r="R8" t="n">
-        <v>7023866</v>
+        <v>7023839</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1479,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,12 +1479,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,17 +1504,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124938398</v>
+        <v>124940176</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>79851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,51 +1527,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446403</v>
+        <v>446236</v>
       </c>
       <c r="R9" t="n">
-        <v>7023878</v>
+        <v>7023806</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,12 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,7 +1611,7 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1652,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937346</v>
+        <v>124940379</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1664,50 +1635,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446466</v>
+        <v>446275</v>
       </c>
       <c r="R10" t="n">
-        <v>7023868</v>
+        <v>7023902</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1736,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1722,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,22 +1742,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937032</v>
+        <v>124936862</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,21 +1770,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1813,10 +1794,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446505</v>
+        <v>446512</v>
       </c>
       <c r="R11" t="n">
-        <v>7023805</v>
+        <v>7023771</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,7 +1829,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1858,12 +1839,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937238</v>
+        <v>124937619</v>
       </c>
       <c r="B12" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,34 +1887,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446500</v>
+        <v>446452</v>
       </c>
       <c r="R12" t="n">
-        <v>7023860</v>
+        <v>7023890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1955,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,12 +1965,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2000,17 +1990,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124936862</v>
+        <v>124936204</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2023,37 +2013,51 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446512</v>
+        <v>446448</v>
       </c>
       <c r="R13" t="n">
-        <v>7023771</v>
+        <v>7023801</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2082,7 +2086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,12 +2096,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,22 +2116,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124937179</v>
+        <v>124936966</v>
       </c>
       <c r="B14" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,38 +2140,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446500</v>
+        <v>446533</v>
       </c>
       <c r="R14" t="n">
-        <v>7023860</v>
+        <v>7023754</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,7 +2217,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2209,12 +2227,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2229,19 +2247,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124935467</v>
+        <v>124937870</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2276,7 +2294,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2284,16 +2302,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446385</v>
+        <v>446461</v>
       </c>
       <c r="R15" t="n">
-        <v>7023868</v>
+        <v>7023883</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2325,7 +2348,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2335,7 +2358,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,22 +2378,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124937870</v>
+        <v>124940260</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2374,55 +2402,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446461</v>
+        <v>446210</v>
       </c>
       <c r="R16" t="n">
-        <v>7023883</v>
+        <v>7023879</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2451,7 +2474,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2461,12 +2484,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,22 +2499,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124937224</v>
+        <v>124937577</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,41 +2523,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446500</v>
+        <v>446475</v>
       </c>
       <c r="R17" t="n">
-        <v>7023860</v>
+        <v>7023891</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2568,7 +2600,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2578,12 +2610,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,17 +2635,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124935567</v>
+        <v>124939729</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2622,30 +2654,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2664,13 +2696,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446418</v>
+        <v>446196</v>
       </c>
       <c r="R18" t="n">
-        <v>7023888</v>
+        <v>7023847</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2699,7 +2731,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2709,12 +2741,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2741,7 +2773,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124937577</v>
+        <v>124940534</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2776,7 +2808,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2791,17 +2823,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446475</v>
+        <v>446314</v>
       </c>
       <c r="R19" t="n">
-        <v>7023891</v>
+        <v>7023930</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2830,7 +2862,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2840,12 +2872,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2860,22 +2887,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124939161</v>
+        <v>124938398</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,25 +2911,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2912,7 +2939,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2921,13 +2953,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446288</v>
+        <v>446403</v>
       </c>
       <c r="R20" t="n">
-        <v>7023859</v>
+        <v>7023878</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2956,7 +2988,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2966,12 +2998,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2998,7 +3030,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124939030</v>
+        <v>124935567</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3033,7 +3065,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3048,17 +3080,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446512</v>
+        <v>446418</v>
       </c>
       <c r="R21" t="n">
-        <v>7023807</v>
+        <v>7023888</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3087,7 +3119,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3097,7 +3129,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3112,7 +3149,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3124,10 +3161,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124936198</v>
+        <v>124937775</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3136,38 +3173,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446431</v>
+        <v>446465</v>
       </c>
       <c r="R22" t="n">
-        <v>7023787</v>
+        <v>7023899</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3199,7 +3245,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3209,12 +3255,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3241,10 +3287,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124939565</v>
+        <v>124936198</v>
       </c>
       <c r="B23" t="n">
-        <v>91700</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3253,25 +3299,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3281,10 +3327,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446214</v>
+        <v>446431</v>
       </c>
       <c r="R23" t="n">
-        <v>7023841</v>
+        <v>7023787</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3316,7 +3362,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3326,12 +3372,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3358,10 +3404,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124936966</v>
+        <v>124938918</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>95335</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3370,52 +3416,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446533</v>
+        <v>446330</v>
       </c>
       <c r="R24" t="n">
-        <v>7023754</v>
+        <v>7023872</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3447,7 +3479,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3457,12 +3489,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>+ 1 vinterståndare</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3477,22 +3509,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124936204</v>
+        <v>124937238</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3505,51 +3537,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446448</v>
+        <v>446500</v>
       </c>
       <c r="R25" t="n">
-        <v>7023801</v>
+        <v>7023860</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3578,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3588,12 +3606,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3608,7 +3626,7 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3620,10 +3638,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124937775</v>
+        <v>124938548</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3632,50 +3650,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446465</v>
+        <v>446512</v>
       </c>
       <c r="R26" t="n">
-        <v>7023899</v>
+        <v>7023807</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3704,7 +3722,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3714,12 +3732,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3734,19 +3747,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124940379</v>
+        <v>124936055</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3781,7 +3794,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3800,13 +3813,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446275</v>
+        <v>446414</v>
       </c>
       <c r="R27" t="n">
-        <v>7023902</v>
+        <v>7023792</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3835,7 +3848,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3845,12 +3858,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3870,17 +3883,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124940260</v>
+        <v>124938507</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>91950</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3889,50 +3902,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446210</v>
+        <v>446376</v>
       </c>
       <c r="R28" t="n">
-        <v>7023879</v>
+        <v>7023866</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3961,7 +3965,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3971,7 +3975,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3986,22 +3995,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124937355</v>
+        <v>124939368</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4010,55 +4019,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446493</v>
+        <v>446236</v>
       </c>
       <c r="R29" t="n">
-        <v>7023830</v>
+        <v>7023806</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4087,7 +4091,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4097,12 +4101,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4117,7 +4116,7 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -4129,10 +4128,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124937619</v>
+        <v>124937179</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4145,43 +4144,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446452</v>
+        <v>446500</v>
       </c>
       <c r="R30" t="n">
-        <v>7023890</v>
+        <v>7023860</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4213,7 +4203,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4223,12 +4213,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4255,10 +4245,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124939368</v>
+        <v>124940281</v>
       </c>
       <c r="B31" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4267,50 +4257,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446236</v>
+        <v>446268</v>
       </c>
       <c r="R31" t="n">
-        <v>7023806</v>
+        <v>7023890</v>
       </c>
       <c r="S31" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4339,7 +4320,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4349,7 +4330,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4364,22 +4350,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124939441</v>
+        <v>124939668</v>
       </c>
       <c r="B32" t="n">
-        <v>95347</v>
+        <v>91008</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4388,25 +4374,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2813</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4416,13 +4402,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446204</v>
+        <v>446191</v>
       </c>
       <c r="R32" t="n">
-        <v>7023839</v>
+        <v>7023833</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4451,7 +4437,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4461,12 +4447,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4493,10 +4479,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124939729</v>
+        <v>124939540</v>
       </c>
       <c r="B33" t="n">
-        <v>98122</v>
+        <v>105102</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4509,38 +4495,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
@@ -4550,7 +4522,7 @@
         <v>446196</v>
       </c>
       <c r="R33" t="n">
-        <v>7023847</v>
+        <v>7023833</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4582,7 +4554,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4592,12 +4564,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4624,10 +4596,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124938916</v>
+        <v>124937355</v>
       </c>
       <c r="B34" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4636,46 +4608,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446512</v>
+        <v>446493</v>
       </c>
       <c r="R34" t="n">
-        <v>7023807</v>
+        <v>7023830</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4704,7 +4685,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4714,7 +4695,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4729,22 +4715,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124939668</v>
+        <v>124939161</v>
       </c>
       <c r="B35" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4757,37 +4743,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446191</v>
+        <v>446288</v>
       </c>
       <c r="R35" t="n">
-        <v>7023833</v>
+        <v>7023859</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4816,7 +4811,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4826,12 +4821,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4858,10 +4853,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124936685</v>
+        <v>124937032</v>
       </c>
       <c r="B36" t="n">
-        <v>91950</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4870,25 +4865,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4898,10 +4893,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446500</v>
+        <v>446505</v>
       </c>
       <c r="R36" t="n">
-        <v>7023715</v>
+        <v>7023805</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4933,7 +4928,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4943,12 +4938,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4975,10 +4970,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124940176</v>
+        <v>124936685</v>
       </c>
       <c r="B37" t="n">
-        <v>79851</v>
+        <v>91950</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4991,37 +4986,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446236</v>
+        <v>446500</v>
       </c>
       <c r="R37" t="n">
-        <v>7023806</v>
+        <v>7023715</v>
       </c>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5050,7 +5045,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5060,7 +5055,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5075,12 +5075,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -3759,10 +3759,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124936055</v>
+        <v>124938507</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3771,55 +3771,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446414</v>
+        <v>446376</v>
       </c>
       <c r="R27" t="n">
-        <v>7023792</v>
+        <v>7023866</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3848,7 +3834,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3858,12 +3844,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3890,7 +3876,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124938507</v>
+        <v>124939368</v>
       </c>
       <c r="B28" t="n">
         <v>91950</v>
@@ -3923,20 +3909,29 @@
           <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446376</v>
+        <v>446236</v>
       </c>
       <c r="R28" t="n">
-        <v>7023866</v>
+        <v>7023806</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3965,7 +3960,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3975,12 +3970,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3995,7 +3985,7 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -4007,10 +3997,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124939368</v>
+        <v>124936055</v>
       </c>
       <c r="B29" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4019,50 +4009,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446236</v>
+        <v>446414</v>
       </c>
       <c r="R29" t="n">
-        <v>7023806</v>
+        <v>7023792</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4091,7 +4086,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4101,7 +4096,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4116,7 +4116,7 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124938916</v>
+        <v>124940281</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446512</v>
+        <v>446268</v>
       </c>
       <c r="R2" t="n">
-        <v>7023807</v>
+        <v>7023890</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124939030</v>
+        <v>124938916</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,40 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -852,7 +843,7 @@
         <v>7023807</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124935467</v>
+        <v>124937032</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,47 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446385</v>
+        <v>446505</v>
       </c>
       <c r="R4" t="n">
-        <v>7023868</v>
+        <v>7023805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124939565</v>
+        <v>124939668</v>
       </c>
       <c r="B5" t="n">
-        <v>91700</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446214</v>
+        <v>446191</v>
       </c>
       <c r="R5" t="n">
-        <v>7023841</v>
+        <v>7023833</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1156,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124937224</v>
+        <v>124937355</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,38 +1155,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446500</v>
+        <v>446493</v>
       </c>
       <c r="R6" t="n">
-        <v>7023860</v>
+        <v>7023830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,12 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937346</v>
+        <v>124939030</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,35 +1286,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,13 +1328,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446466</v>
+        <v>446512</v>
       </c>
       <c r="R7" t="n">
-        <v>7023868</v>
+        <v>7023807</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939441</v>
+        <v>124937224</v>
       </c>
       <c r="B8" t="n">
-        <v>95347</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,25 +1412,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1434,13 +1440,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446204</v>
+        <v>446500</v>
       </c>
       <c r="R8" t="n">
-        <v>7023839</v>
+        <v>7023860</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,12 +1485,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,17 +1510,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124940176</v>
+        <v>124937870</v>
       </c>
       <c r="B9" t="n">
-        <v>79851</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,41 +1529,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446236</v>
+        <v>446461</v>
       </c>
       <c r="R9" t="n">
-        <v>7023806</v>
+        <v>7023883</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,7 +1606,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1616,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,19 +1636,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124940379</v>
+        <v>124937577</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1658,7 +1683,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1677,13 +1702,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446275</v>
+        <v>446475</v>
       </c>
       <c r="R10" t="n">
-        <v>7023902</v>
+        <v>7023891</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1712,7 +1737,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,12 +1747,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,17 +1772,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124936862</v>
+        <v>124940176</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,41 +1791,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446512</v>
+        <v>446236</v>
       </c>
       <c r="R11" t="n">
-        <v>7023771</v>
+        <v>7023806</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1829,7 +1854,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,12 +1864,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,22 +1879,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937619</v>
+        <v>124936055</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,35 +1903,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1920,13 +1945,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446452</v>
+        <v>446414</v>
       </c>
       <c r="R12" t="n">
-        <v>7023890</v>
+        <v>7023792</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1955,7 +1980,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1965,12 +1990,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,17 +2015,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124936204</v>
+        <v>124939161</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,51 +2038,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446448</v>
+        <v>446288</v>
       </c>
       <c r="R13" t="n">
-        <v>7023801</v>
+        <v>7023859</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2086,7 +2106,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,12 +2116,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,22 +2136,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124936966</v>
+        <v>124937346</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2140,40 +2160,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2182,13 +2197,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446533</v>
+        <v>446466</v>
       </c>
       <c r="R14" t="n">
-        <v>7023754</v>
+        <v>7023868</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2217,7 +2232,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2227,12 +2242,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:34</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>+ 1 vinterståndare</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2259,10 +2269,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124937870</v>
+        <v>124936685</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,52 +2281,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446461</v>
+        <v>446500</v>
       </c>
       <c r="R15" t="n">
-        <v>7023883</v>
+        <v>7023715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2348,7 +2344,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2511,10 +2507,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124937577</v>
+        <v>124939565</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2523,55 +2519,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446475</v>
+        <v>446214</v>
       </c>
       <c r="R17" t="n">
-        <v>7023891</v>
+        <v>7023841</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2600,7 +2582,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2610,12 +2592,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2635,17 +2617,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124939729</v>
+        <v>124938398</v>
       </c>
       <c r="B18" t="n">
-        <v>98122</v>
+        <v>100279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2658,21 +2640,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2687,7 +2669,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2696,10 +2678,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446196</v>
+        <v>446403</v>
       </c>
       <c r="R18" t="n">
-        <v>7023847</v>
+        <v>7023878</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2731,7 +2713,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,12 +2723,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2899,10 +2881,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124938398</v>
+        <v>124935567</v>
       </c>
       <c r="B20" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2911,30 +2893,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2944,7 +2926,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2953,13 +2935,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446403</v>
+        <v>446418</v>
       </c>
       <c r="R20" t="n">
-        <v>7023878</v>
+        <v>7023888</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2988,7 +2970,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2998,12 +2980,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3030,10 +3012,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124935567</v>
+        <v>124937238</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3042,55 +3024,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446418</v>
+        <v>446500</v>
       </c>
       <c r="R21" t="n">
-        <v>7023888</v>
+        <v>7023860</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3119,7 +3087,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3129,12 +3097,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,17 +3122,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124937775</v>
+        <v>124938507</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3173,47 +3141,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446465</v>
+        <v>446376</v>
       </c>
       <c r="R22" t="n">
-        <v>7023899</v>
+        <v>7023866</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3245,7 +3204,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3255,12 +3214,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3287,10 +3246,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124936198</v>
+        <v>124935467</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3299,38 +3258,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446431</v>
+        <v>446385</v>
       </c>
       <c r="R23" t="n">
-        <v>7023787</v>
+        <v>7023868</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3362,7 +3330,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3372,12 +3340,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3392,22 +3355,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124938918</v>
+        <v>124936862</v>
       </c>
       <c r="B24" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3416,25 +3379,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3444,10 +3407,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446330</v>
+        <v>446512</v>
       </c>
       <c r="R24" t="n">
-        <v>7023872</v>
+        <v>7023771</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3479,7 +3442,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3489,12 +3452,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3521,10 +3484,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124937238</v>
+        <v>124936204</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3537,37 +3500,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446500</v>
+        <v>446448</v>
       </c>
       <c r="R25" t="n">
-        <v>7023860</v>
+        <v>7023801</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3596,7 +3573,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,12 +3583,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3626,7 +3603,7 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3638,10 +3615,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124938548</v>
+        <v>124939729</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>98122</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3654,21 +3631,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3676,24 +3653,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446512</v>
+        <v>446196</v>
       </c>
       <c r="R26" t="n">
-        <v>7023807</v>
+        <v>7023847</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3722,7 +3704,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3732,7 +3714,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3747,22 +3734,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124938507</v>
+        <v>124938548</v>
       </c>
       <c r="B27" t="n">
-        <v>91950</v>
+        <v>57883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3775,37 +3762,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446376</v>
+        <v>446512</v>
       </c>
       <c r="R27" t="n">
-        <v>7023866</v>
+        <v>7023807</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3834,7 +3830,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3844,12 +3840,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3864,22 +3855,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124939368</v>
+        <v>124939540</v>
       </c>
       <c r="B28" t="n">
-        <v>91950</v>
+        <v>105102</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3892,46 +3883,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446236</v>
+        <v>446196</v>
       </c>
       <c r="R28" t="n">
-        <v>7023806</v>
+        <v>7023833</v>
       </c>
       <c r="S28" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3960,7 +3942,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3970,7 +3952,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3985,7 +3972,7 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3997,10 +3984,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124936055</v>
+        <v>124936198</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4009,55 +3996,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446414</v>
+        <v>446431</v>
       </c>
       <c r="R29" t="n">
-        <v>7023792</v>
+        <v>7023787</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4086,7 +4059,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4096,12 +4069,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4128,10 +4101,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124937179</v>
+        <v>124940379</v>
       </c>
       <c r="B30" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4140,38 +4113,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446500</v>
+        <v>446275</v>
       </c>
       <c r="R30" t="n">
-        <v>7023860</v>
+        <v>7023902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4203,7 +4190,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4213,12 +4200,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4238,17 +4225,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124940281</v>
+        <v>124936966</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4257,41 +4244,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446268</v>
+        <v>446533</v>
       </c>
       <c r="R31" t="n">
-        <v>7023890</v>
+        <v>7023754</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4320,7 +4321,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4330,12 +4331,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4350,22 +4351,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124939668</v>
+        <v>124937619</v>
       </c>
       <c r="B32" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4378,34 +4379,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446191</v>
+        <v>446452</v>
       </c>
       <c r="R32" t="n">
-        <v>7023833</v>
+        <v>7023890</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4437,7 +4447,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4447,12 +4457,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4479,10 +4489,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124939540</v>
+        <v>124939368</v>
       </c>
       <c r="B33" t="n">
-        <v>105102</v>
+        <v>91950</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4495,37 +4505,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221725</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446196</v>
+        <v>446236</v>
       </c>
       <c r="R33" t="n">
-        <v>7023833</v>
+        <v>7023806</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4554,7 +4573,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4564,12 +4583,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4584,22 +4598,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124937355</v>
+        <v>124938918</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>95335</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4608,52 +4622,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446493</v>
+        <v>446330</v>
       </c>
       <c r="R34" t="n">
-        <v>7023830</v>
+        <v>7023872</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4727,10 +4727,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124939161</v>
+        <v>124937179</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4743,46 +4743,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446288</v>
+        <v>446500</v>
       </c>
       <c r="R35" t="n">
-        <v>7023859</v>
+        <v>7023860</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4811,7 +4802,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4821,12 +4812,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4853,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124937032</v>
+        <v>124939441</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>95347</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4865,25 +4856,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4893,13 +4884,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446505</v>
+        <v>446204</v>
       </c>
       <c r="R36" t="n">
-        <v>7023805</v>
+        <v>7023839</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4928,7 +4919,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4938,12 +4929,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4970,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124936685</v>
+        <v>124937775</v>
       </c>
       <c r="B37" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4982,38 +4973,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446500</v>
+        <v>446465</v>
       </c>
       <c r="R37" t="n">
-        <v>7023715</v>
+        <v>7023899</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -3129,10 +3129,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124938507</v>
+        <v>124935467</v>
       </c>
       <c r="B22" t="n">
-        <v>91950</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3141,38 +3141,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446376</v>
+        <v>446385</v>
       </c>
       <c r="R22" t="n">
-        <v>7023866</v>
+        <v>7023868</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3204,7 +3213,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3214,12 +3223,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3234,22 +3238,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124935467</v>
+        <v>124938507</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>91950</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3258,47 +3262,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446385</v>
+        <v>446376</v>
       </c>
       <c r="R23" t="n">
-        <v>7023868</v>
+        <v>7023866</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3330,7 +3325,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3340,7 +3335,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3355,22 +3355,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124936862</v>
+        <v>124938548</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3379,41 +3379,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
         <v>446512</v>
       </c>
       <c r="R24" t="n">
-        <v>7023771</v>
+        <v>7023807</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3442,7 +3451,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3452,12 +3461,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3472,22 +3476,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124936204</v>
+        <v>124939729</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>98122</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3496,55 +3500,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446448</v>
+        <v>446196</v>
       </c>
       <c r="R25" t="n">
-        <v>7023801</v>
+        <v>7023847</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3573,7 +3577,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3583,12 +3587,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,22 +3607,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124939729</v>
+        <v>124936862</v>
       </c>
       <c r="B26" t="n">
-        <v>98122</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3627,52 +3631,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446196</v>
+        <v>446512</v>
       </c>
       <c r="R26" t="n">
-        <v>7023847</v>
+        <v>7023771</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3704,7 +3694,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3714,12 +3704,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3746,10 +3736,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124938548</v>
+        <v>124936204</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3758,35 +3748,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3795,13 +3790,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446512</v>
+        <v>446448</v>
       </c>
       <c r="R27" t="n">
-        <v>7023807</v>
+        <v>7023801</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3830,7 +3825,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3840,7 +3835,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3867,10 +3867,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124939540</v>
+        <v>124936198</v>
       </c>
       <c r="B28" t="n">
-        <v>105102</v>
+        <v>74901</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3879,25 +3879,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446196</v>
+        <v>446431</v>
       </c>
       <c r="R28" t="n">
-        <v>7023833</v>
+        <v>7023787</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124936198</v>
+        <v>124939540</v>
       </c>
       <c r="B29" t="n">
-        <v>74901</v>
+        <v>105102</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3996,25 +3996,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446431</v>
+        <v>446196</v>
       </c>
       <c r="R29" t="n">
-        <v>7023787</v>
+        <v>7023833</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124940281</v>
+        <v>124937224</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446268</v>
+        <v>446500</v>
       </c>
       <c r="R2" t="n">
-        <v>7023890</v>
+        <v>7023860</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124938916</v>
+        <v>124937619</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,46 +804,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446512</v>
+        <v>446452</v>
       </c>
       <c r="R3" t="n">
-        <v>7023807</v>
+        <v>7023890</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +906,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124937032</v>
+        <v>124938918</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>95335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +930,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446505</v>
+        <v>446330</v>
       </c>
       <c r="R4" t="n">
-        <v>7023805</v>
+        <v>7023872</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124939668</v>
+        <v>124935467</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1047,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446191</v>
+        <v>446385</v>
       </c>
       <c r="R5" t="n">
-        <v>7023833</v>
+        <v>7023868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1144,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1143,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124937355</v>
+        <v>124936966</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1178,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1193,14 +1206,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446493</v>
+        <v>446533</v>
       </c>
       <c r="R6" t="n">
-        <v>7023830</v>
+        <v>7023754</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1255,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1275,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1274,7 +1287,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939030</v>
+        <v>124937355</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1309,7 +1322,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1324,14 +1337,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446512</v>
+        <v>446493</v>
       </c>
       <c r="R7" t="n">
-        <v>7023807</v>
+        <v>7023830</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1386,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,22 +1406,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937224</v>
+        <v>124937775</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,38 +1430,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446500</v>
+        <v>446465</v>
       </c>
       <c r="R8" t="n">
-        <v>7023860</v>
+        <v>7023899</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,7 +1502,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,12 +1512,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,14 +1537,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937870</v>
+        <v>124939030</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1552,7 +1579,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1567,14 +1594,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446461</v>
+        <v>446512</v>
       </c>
       <c r="R9" t="n">
-        <v>7023883</v>
+        <v>7023807</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,7 +1633,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1616,12 +1643,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,19 +1658,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937577</v>
+        <v>124936055</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1683,7 +1705,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1702,10 +1724,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446475</v>
+        <v>446414</v>
       </c>
       <c r="R10" t="n">
-        <v>7023891</v>
+        <v>7023792</v>
       </c>
       <c r="S10" t="n">
         <v>7</v>
@@ -1737,7 +1759,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1747,12 +1769,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1801,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124940176</v>
+        <v>124935567</v>
       </c>
       <c r="B11" t="n">
-        <v>79851</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1791,41 +1813,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446236</v>
+        <v>446418</v>
       </c>
       <c r="R11" t="n">
-        <v>7023806</v>
+        <v>7023888</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1854,7 +1890,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1864,7 +1900,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1879,19 +1920,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124936055</v>
+        <v>124937870</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1926,7 +1967,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1945,13 +1986,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446414</v>
+        <v>446461</v>
       </c>
       <c r="R12" t="n">
-        <v>7023792</v>
+        <v>7023883</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1980,7 +2021,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1990,12 +2031,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2022,10 +2063,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124939161</v>
+        <v>124938507</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2034,50 +2075,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446288</v>
+        <v>446376</v>
       </c>
       <c r="R13" t="n">
-        <v>7023859</v>
+        <v>7023866</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2106,7 +2138,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2116,12 +2148,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,10 +2180,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124937346</v>
+        <v>124939441</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>95347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,50 +2192,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446466</v>
+        <v>446204</v>
       </c>
       <c r="R14" t="n">
-        <v>7023868</v>
+        <v>7023839</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2232,7 +2255,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2242,7 +2265,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2257,22 +2285,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124936685</v>
+        <v>124939540</v>
       </c>
       <c r="B15" t="n">
-        <v>91950</v>
+        <v>105102</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2285,21 +2313,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2309,10 +2337,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446500</v>
+        <v>446196</v>
       </c>
       <c r="R15" t="n">
-        <v>7023715</v>
+        <v>7023833</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2344,7 +2372,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2354,12 +2382,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2386,10 +2414,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124940260</v>
+        <v>124937032</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2402,46 +2430,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446210</v>
+        <v>446505</v>
       </c>
       <c r="R16" t="n">
-        <v>7023879</v>
+        <v>7023805</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2470,7 +2489,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2480,7 +2499,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2495,22 +2519,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124939565</v>
+        <v>124939368</v>
       </c>
       <c r="B17" t="n">
-        <v>91700</v>
+        <v>91950</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2523,37 +2547,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446214</v>
+        <v>446236</v>
       </c>
       <c r="R17" t="n">
-        <v>7023841</v>
+        <v>7023806</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2582,7 +2615,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2592,12 +2625,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2612,22 +2640,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124938398</v>
+        <v>124940281</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2636,55 +2664,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446403</v>
+        <v>446268</v>
       </c>
       <c r="R18" t="n">
-        <v>7023878</v>
+        <v>7023890</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2713,7 +2727,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2723,12 +2737,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,10 +2769,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124940534</v>
+        <v>124937346</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2767,40 +2781,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2809,13 +2818,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446314</v>
+        <v>446466</v>
       </c>
       <c r="R19" t="n">
-        <v>7023930</v>
+        <v>7023868</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2844,7 +2853,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2854,7 +2863,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2881,10 +2890,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124935567</v>
+        <v>124940260</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2893,55 +2902,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446418</v>
+        <v>446210</v>
       </c>
       <c r="R20" t="n">
-        <v>7023888</v>
+        <v>7023879</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2970,7 +2974,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2980,12 +2984,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3000,22 +2999,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124937238</v>
+        <v>124939161</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3028,37 +3027,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446500</v>
+        <v>446288</v>
       </c>
       <c r="R21" t="n">
-        <v>7023860</v>
+        <v>7023859</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3087,7 +3095,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3097,12 +3105,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3129,10 +3137,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124935467</v>
+        <v>124940176</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>79851</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3141,50 +3149,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446385</v>
+        <v>446236</v>
       </c>
       <c r="R22" t="n">
-        <v>7023868</v>
+        <v>7023806</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3213,7 +3212,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3223,7 +3222,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3250,10 +3249,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124938507</v>
+        <v>124939668</v>
       </c>
       <c r="B23" t="n">
-        <v>91950</v>
+        <v>91008</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3262,25 +3261,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3290,10 +3289,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446376</v>
+        <v>446191</v>
       </c>
       <c r="R23" t="n">
-        <v>7023866</v>
+        <v>7023833</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3325,7 +3324,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3335,12 +3334,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3367,10 +3366,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124938548</v>
+        <v>124936685</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>91950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3383,46 +3382,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446512</v>
+        <v>446500</v>
       </c>
       <c r="R24" t="n">
-        <v>7023807</v>
+        <v>7023715</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3451,7 +3441,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3461,7 +3451,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3476,22 +3471,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124939729</v>
+        <v>124936862</v>
       </c>
       <c r="B25" t="n">
-        <v>98122</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3500,52 +3495,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446196</v>
+        <v>446512</v>
       </c>
       <c r="R25" t="n">
-        <v>7023847</v>
+        <v>7023771</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3577,7 +3558,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3587,12 +3568,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3612,17 +3593,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124936862</v>
+        <v>124936204</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3635,37 +3616,51 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446512</v>
+        <v>446448</v>
       </c>
       <c r="R26" t="n">
-        <v>7023771</v>
+        <v>7023801</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3694,7 +3689,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3704,12 +3699,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3724,22 +3719,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124936204</v>
+        <v>124938548</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3748,40 +3743,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3790,13 +3780,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446448</v>
+        <v>446512</v>
       </c>
       <c r="R27" t="n">
-        <v>7023801</v>
+        <v>7023807</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3825,7 +3815,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3835,12 +3825,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3867,10 +3852,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124936198</v>
+        <v>124940379</v>
       </c>
       <c r="B28" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3879,38 +3864,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446431</v>
+        <v>446275</v>
       </c>
       <c r="R28" t="n">
-        <v>7023787</v>
+        <v>7023902</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3942,7 +3941,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3952,12 +3951,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3977,17 +3976,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124939540</v>
+        <v>124940534</v>
       </c>
       <c r="B29" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3996,41 +3995,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446196</v>
+        <v>446314</v>
       </c>
       <c r="R29" t="n">
-        <v>7023833</v>
+        <v>7023930</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4059,7 +4072,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4069,12 +4082,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4089,22 +4097,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124940379</v>
+        <v>124938398</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4113,30 +4121,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4146,7 +4154,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4155,10 +4163,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446275</v>
+        <v>446403</v>
       </c>
       <c r="R30" t="n">
-        <v>7023902</v>
+        <v>7023878</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4190,7 +4198,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4200,12 +4208,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4225,17 +4233,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124936966</v>
+        <v>124938916</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4244,40 +4252,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4286,13 +4285,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446533</v>
+        <v>446512</v>
       </c>
       <c r="R31" t="n">
-        <v>7023754</v>
+        <v>7023807</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4321,7 +4320,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4331,12 +4330,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:34</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>+ 1 vinterståndare</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4363,10 +4357,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124937619</v>
+        <v>124936198</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4379,43 +4373,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446452</v>
+        <v>446431</v>
       </c>
       <c r="R32" t="n">
-        <v>7023890</v>
+        <v>7023787</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4447,7 +4432,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4457,12 +4442,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4489,10 +4474,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124939368</v>
+        <v>124937179</v>
       </c>
       <c r="B33" t="n">
-        <v>91950</v>
+        <v>77743</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4501,50 +4486,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446236</v>
+        <v>446500</v>
       </c>
       <c r="R33" t="n">
-        <v>7023806</v>
+        <v>7023860</v>
       </c>
       <c r="S33" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4573,7 +4549,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4583,7 +4559,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4598,22 +4579,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124938918</v>
+        <v>124937577</v>
       </c>
       <c r="B34" t="n">
-        <v>95335</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4622,41 +4603,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446330</v>
+        <v>446475</v>
       </c>
       <c r="R34" t="n">
-        <v>7023872</v>
+        <v>7023891</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4685,7 +4680,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4695,12 +4690,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4727,10 +4722,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124937179</v>
+        <v>124937238</v>
       </c>
       <c r="B35" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4743,21 +4738,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4802,7 +4797,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4812,12 +4807,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4844,10 +4839,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124939441</v>
+        <v>124939729</v>
       </c>
       <c r="B36" t="n">
-        <v>95347</v>
+        <v>98122</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4860,37 +4855,51 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2813</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446204</v>
+        <v>446196</v>
       </c>
       <c r="R36" t="n">
-        <v>7023839</v>
+        <v>7023847</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4919,7 +4928,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4929,12 +4938,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4961,10 +4970,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124937775</v>
+        <v>124939565</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>91700</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4973,47 +4982,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446465</v>
+        <v>446214</v>
       </c>
       <c r="R37" t="n">
-        <v>7023899</v>
+        <v>7023841</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124937224</v>
+        <v>124939540</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>105278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446500</v>
+        <v>446196</v>
       </c>
       <c r="R2" t="n">
-        <v>7023860</v>
+        <v>7023833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124937619</v>
+        <v>124938918</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>95503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,47 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446452</v>
+        <v>446330</v>
       </c>
       <c r="R3" t="n">
-        <v>7023890</v>
+        <v>7023872</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,17 +902,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124938918</v>
+        <v>124937224</v>
       </c>
       <c r="B4" t="n">
-        <v>95335</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446330</v>
+        <v>446500</v>
       </c>
       <c r="R4" t="n">
-        <v>7023872</v>
+        <v>7023860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124935467</v>
+        <v>124936204</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91184</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,35 +1038,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446385</v>
+        <v>446448</v>
       </c>
       <c r="R5" t="n">
-        <v>7023868</v>
+        <v>7023801</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,17 +1150,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124936966</v>
+        <v>124939030</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,7 +1192,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1210,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446533</v>
+        <v>446512</v>
       </c>
       <c r="R6" t="n">
-        <v>7023754</v>
+        <v>7023807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,12 +1256,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:34</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>+ 1 vinterståndare</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,17 +1276,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937355</v>
+        <v>124939565</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91860</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,52 +1295,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446493</v>
+        <v>446214</v>
       </c>
       <c r="R7" t="n">
-        <v>7023830</v>
+        <v>7023841</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1376,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,12 +1368,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937775</v>
+        <v>124938398</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>100451</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,30 +1412,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1461,16 +1443,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446465</v>
+        <v>446403</v>
       </c>
       <c r="R8" t="n">
-        <v>7023899</v>
+        <v>7023878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,12 +1499,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,17 +1524,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939030</v>
+        <v>124939668</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91162</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,52 +1543,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446512</v>
+        <v>446191</v>
       </c>
       <c r="R9" t="n">
-        <v>7023807</v>
+        <v>7023833</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,7 +1606,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1643,7 +1616,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,22 +1636,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124936055</v>
+        <v>124937238</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>75025</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1682,55 +1660,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446414</v>
+        <v>446500</v>
       </c>
       <c r="R10" t="n">
-        <v>7023792</v>
+        <v>7023860</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,12 +1733,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1801,10 +1765,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124935567</v>
+        <v>124938548</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>58001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1813,55 +1777,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446418</v>
+        <v>446512</v>
       </c>
       <c r="R11" t="n">
-        <v>7023888</v>
+        <v>7023807</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1890,7 +1849,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1900,12 +1859,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,22 +1874,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937870</v>
+        <v>124940281</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1944,55 +1898,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446461</v>
+        <v>446268</v>
       </c>
       <c r="R12" t="n">
-        <v>7023883</v>
+        <v>7023890</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2021,7 +1961,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2031,12 +1971,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2063,10 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124938507</v>
+        <v>124939368</v>
       </c>
       <c r="B13" t="n">
-        <v>91950</v>
+        <v>92098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,23 +2033,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446376</v>
+        <v>446236</v>
       </c>
       <c r="R13" t="n">
-        <v>7023866</v>
+        <v>7023806</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2138,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2148,12 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2168,22 +2112,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124939441</v>
+        <v>124936862</v>
       </c>
       <c r="B14" t="n">
-        <v>95347</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2192,25 +2136,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2220,13 +2164,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446204</v>
+        <v>446512</v>
       </c>
       <c r="R14" t="n">
-        <v>7023839</v>
+        <v>7023771</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2255,7 +2199,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2265,12 +2209,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2297,10 +2241,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124939540</v>
+        <v>124937032</v>
       </c>
       <c r="B15" t="n">
-        <v>105102</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2309,25 +2253,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2337,10 +2281,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446196</v>
+        <v>446505</v>
       </c>
       <c r="R15" t="n">
-        <v>7023833</v>
+        <v>7023805</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2372,7 +2316,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2382,12 +2326,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2414,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124937032</v>
+        <v>124937577</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2426,41 +2370,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446505</v>
+        <v>446475</v>
       </c>
       <c r="R16" t="n">
-        <v>7023805</v>
+        <v>7023891</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2489,7 +2447,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2499,12 +2457,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2531,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124939368</v>
+        <v>124938507</v>
       </c>
       <c r="B17" t="n">
-        <v>91950</v>
+        <v>92098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2561,32 +2519,23 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446236</v>
+        <v>446376</v>
       </c>
       <c r="R17" t="n">
-        <v>7023806</v>
+        <v>7023866</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2615,7 +2564,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2625,7 +2574,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2640,22 +2594,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124940281</v>
+        <v>124938916</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>56836</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,41 +2618,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446268</v>
+        <v>446512</v>
       </c>
       <c r="R18" t="n">
-        <v>7023890</v>
+        <v>7023807</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2727,7 +2686,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2737,12 +2696,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2757,7 +2711,7 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2769,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124937346</v>
+        <v>124940260</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57793</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2785,46 +2739,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446466</v>
+        <v>446210</v>
       </c>
       <c r="R19" t="n">
-        <v>7023868</v>
+        <v>7023879</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2853,7 +2807,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2863,7 +2817,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2890,10 +2844,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124940260</v>
+        <v>124940176</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>79988</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2902,50 +2856,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446210</v>
+        <v>446236</v>
       </c>
       <c r="R20" t="n">
-        <v>7023879</v>
+        <v>7023806</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2974,7 +2919,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2984,7 +2929,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3011,10 +2956,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124939161</v>
+        <v>124935467</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3023,50 +2968,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446288</v>
+        <v>446385</v>
       </c>
       <c r="R21" t="n">
-        <v>7023859</v>
+        <v>7023868</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3095,7 +3040,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3105,12 +3050,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3125,22 +3065,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124940176</v>
+        <v>124937619</v>
       </c>
       <c r="B22" t="n">
-        <v>79851</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3149,41 +3089,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446236</v>
+        <v>446452</v>
       </c>
       <c r="R22" t="n">
-        <v>7023806</v>
+        <v>7023890</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3212,7 +3161,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3222,7 +3171,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3237,22 +3191,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124939668</v>
+        <v>124937775</v>
       </c>
       <c r="B23" t="n">
-        <v>91008</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3261,38 +3215,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446191</v>
+        <v>446465</v>
       </c>
       <c r="R23" t="n">
-        <v>7023833</v>
+        <v>7023899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3324,7 +3287,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3334,12 +3297,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3366,10 +3329,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124936685</v>
+        <v>124939441</v>
       </c>
       <c r="B24" t="n">
-        <v>91950</v>
+        <v>95515</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3382,21 +3345,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>2813</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3406,13 +3369,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446500</v>
+        <v>446204</v>
       </c>
       <c r="R24" t="n">
-        <v>7023715</v>
+        <v>7023839</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3441,7 +3404,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3451,12 +3414,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3483,10 +3446,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124936862</v>
+        <v>124940379</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3495,38 +3458,52 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446512</v>
+        <v>446275</v>
       </c>
       <c r="R25" t="n">
-        <v>7023771</v>
+        <v>7023902</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3558,7 +3535,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3568,12 +3545,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3593,17 +3570,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124936204</v>
+        <v>124935567</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3612,52 +3589,52 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446448</v>
+        <v>446418</v>
       </c>
       <c r="R26" t="n">
-        <v>7023801</v>
+        <v>7023888</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -3689,7 +3666,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3699,12 +3676,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3719,22 +3696,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124938548</v>
+        <v>124936685</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>92098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3747,46 +3724,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446512</v>
+        <v>446500</v>
       </c>
       <c r="R27" t="n">
-        <v>7023807</v>
+        <v>7023715</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3815,7 +3783,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3825,7 +3793,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3840,22 +3813,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124940379</v>
+        <v>124936966</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3887,7 +3860,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3902,14 +3875,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446275</v>
+        <v>446533</v>
       </c>
       <c r="R28" t="n">
-        <v>7023902</v>
+        <v>7023754</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3941,7 +3914,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3951,12 +3924,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3971,12 +3944,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3986,7 +3959,7 @@
         <v>124940534</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4109,10 +4082,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124938398</v>
+        <v>124936055</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>98269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4121,30 +4094,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4154,7 +4127,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4163,13 +4136,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446403</v>
+        <v>446414</v>
       </c>
       <c r="R30" t="n">
-        <v>7023878</v>
+        <v>7023792</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4198,7 +4171,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4208,12 +4181,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4240,10 +4213,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124938916</v>
+        <v>124937355</v>
       </c>
       <c r="B31" t="n">
-        <v>56722</v>
+        <v>98269</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4252,46 +4225,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446512</v>
+        <v>446493</v>
       </c>
       <c r="R31" t="n">
-        <v>7023807</v>
+        <v>7023830</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4320,7 +4302,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4330,7 +4312,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4345,12 +4332,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4360,7 +4347,7 @@
         <v>124936198</v>
       </c>
       <c r="B32" t="n">
-        <v>74901</v>
+        <v>75025</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4474,10 +4461,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124937179</v>
+        <v>124939729</v>
       </c>
       <c r="B33" t="n">
-        <v>77743</v>
+        <v>98290</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4486,38 +4473,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446500</v>
+        <v>446196</v>
       </c>
       <c r="R33" t="n">
-        <v>7023860</v>
+        <v>7023847</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4549,7 +4550,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4559,12 +4560,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4591,10 +4592,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124937577</v>
+        <v>124937870</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4626,7 +4627,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4645,13 +4646,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446475</v>
+        <v>446461</v>
       </c>
       <c r="R34" t="n">
-        <v>7023891</v>
+        <v>7023883</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4680,7 +4681,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4690,12 +4691,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4722,10 +4723,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124937238</v>
+        <v>124937346</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>78947</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4738,37 +4739,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446500</v>
+        <v>446466</v>
       </c>
       <c r="R35" t="n">
-        <v>7023860</v>
+        <v>7023868</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4797,7 +4807,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4807,12 +4817,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4827,22 +4832,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124939729</v>
+        <v>124939161</v>
       </c>
       <c r="B36" t="n">
-        <v>98122</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4851,25 +4856,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4879,12 +4884,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4893,13 +4893,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446196</v>
+        <v>446288</v>
       </c>
       <c r="R36" t="n">
-        <v>7023847</v>
+        <v>7023859</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4970,10 +4970,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124939565</v>
+        <v>124937179</v>
       </c>
       <c r="B37" t="n">
-        <v>91700</v>
+        <v>77879</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4982,25 +4982,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446214</v>
+        <v>446500</v>
       </c>
       <c r="R37" t="n">
-        <v>7023841</v>
+        <v>7023860</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -2003,10 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124939368</v>
+        <v>124937577</v>
       </c>
       <c r="B13" t="n">
-        <v>92098</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2015,50 +2015,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446236</v>
+        <v>446475</v>
       </c>
       <c r="R13" t="n">
-        <v>7023806</v>
+        <v>7023891</v>
       </c>
       <c r="S13" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,22 +2122,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124936862</v>
+        <v>124939368</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
+        <v>92098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,41 +2146,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446512</v>
+        <v>446236</v>
       </c>
       <c r="R14" t="n">
-        <v>7023771</v>
+        <v>7023806</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2199,7 +2218,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2209,12 +2228,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2229,22 +2243,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124937032</v>
+        <v>124936862</v>
       </c>
       <c r="B15" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,21 +2271,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2281,10 +2295,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446505</v>
+        <v>446512</v>
       </c>
       <c r="R15" t="n">
-        <v>7023805</v>
+        <v>7023771</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2316,7 +2330,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2326,12 +2340,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124937577</v>
+        <v>124937032</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,55 +2384,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446475</v>
+        <v>446505</v>
       </c>
       <c r="R16" t="n">
-        <v>7023891</v>
+        <v>7023805</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124939540</v>
+        <v>124940176</v>
       </c>
       <c r="B2" t="n">
-        <v>105278</v>
+        <v>79988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446196</v>
+        <v>446236</v>
       </c>
       <c r="R2" t="n">
-        <v>7023833</v>
+        <v>7023806</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124938918</v>
+        <v>124939441</v>
       </c>
       <c r="B3" t="n">
-        <v>95503</v>
+        <v>95515</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446330</v>
+        <v>446204</v>
       </c>
       <c r="R3" t="n">
-        <v>7023872</v>
+        <v>7023839</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,14 +897,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124937224</v>
+        <v>124937619</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
@@ -942,17 +937,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446500</v>
+        <v>446452</v>
       </c>
       <c r="R4" t="n">
-        <v>7023860</v>
+        <v>7023890</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124936204</v>
+        <v>124936685</v>
       </c>
       <c r="B5" t="n">
-        <v>91184</v>
+        <v>92098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,55 +1042,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446448</v>
+        <v>446500</v>
       </c>
       <c r="R5" t="n">
-        <v>7023801</v>
+        <v>7023715</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,19 +1135,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124939030</v>
+        <v>124937355</v>
       </c>
       <c r="B6" t="n">
         <v>98269</v>
@@ -1192,7 +1182,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1207,14 +1197,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446512</v>
+        <v>446493</v>
       </c>
       <c r="R6" t="n">
-        <v>7023807</v>
+        <v>7023830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,7 +1246,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,22 +1266,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939565</v>
+        <v>124937179</v>
       </c>
       <c r="B7" t="n">
-        <v>91860</v>
+        <v>77879</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,25 +1290,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446214</v>
+        <v>446500</v>
       </c>
       <c r="R7" t="n">
-        <v>7023841</v>
+        <v>7023860</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,12 +1363,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124938398</v>
+        <v>124939030</v>
       </c>
       <c r="B8" t="n">
-        <v>100451</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,30 +1407,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1445,19 +1440,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446403</v>
+        <v>446512</v>
       </c>
       <c r="R8" t="n">
-        <v>7023878</v>
+        <v>7023807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1489,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,12 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,22 +1509,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939668</v>
+        <v>124937870</v>
       </c>
       <c r="B9" t="n">
-        <v>91162</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,38 +1533,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446191</v>
+        <v>446461</v>
       </c>
       <c r="R9" t="n">
-        <v>7023833</v>
+        <v>7023883</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1616,12 +1620,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,10 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937238</v>
+        <v>124939565</v>
       </c>
       <c r="B10" t="n">
-        <v>75025</v>
+        <v>91860</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,25 +1664,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1688,10 +1692,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446500</v>
+        <v>446214</v>
       </c>
       <c r="R10" t="n">
-        <v>7023860</v>
+        <v>7023841</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,7 +1727,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,12 +1737,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,10 +1769,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124938548</v>
+        <v>124937032</v>
       </c>
       <c r="B11" t="n">
-        <v>58001</v>
+        <v>91166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1777,50 +1781,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446512</v>
+        <v>446505</v>
       </c>
       <c r="R11" t="n">
-        <v>7023807</v>
+        <v>7023805</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1849,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,7 +1854,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,19 +1874,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124940281</v>
+        <v>124937224</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446268</v>
+        <v>446500</v>
       </c>
       <c r="R12" t="n">
-        <v>7023890</v>
+        <v>7023860</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2003,7 +2003,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124937577</v>
+        <v>124940379</v>
       </c>
       <c r="B13" t="n">
         <v>98269</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446475</v>
+        <v>446275</v>
       </c>
       <c r="R13" t="n">
-        <v>7023891</v>
+        <v>7023902</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,17 +2127,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124939368</v>
+        <v>124935567</v>
       </c>
       <c r="B14" t="n">
-        <v>92098</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,50 +2146,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446236</v>
+        <v>446418</v>
       </c>
       <c r="R14" t="n">
-        <v>7023806</v>
+        <v>7023888</v>
       </c>
       <c r="S14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2218,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2228,7 +2233,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,22 +2253,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124936862</v>
+        <v>124937577</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2267,41 +2277,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446512</v>
+        <v>446475</v>
       </c>
       <c r="R15" t="n">
-        <v>7023771</v>
+        <v>7023891</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2330,7 +2354,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2340,12 +2364,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,10 +2396,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124937032</v>
+        <v>124940281</v>
       </c>
       <c r="B16" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,21 +2412,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2412,13 +2436,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446505</v>
+        <v>446268</v>
       </c>
       <c r="R16" t="n">
-        <v>7023805</v>
+        <v>7023890</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2447,7 +2471,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2457,12 +2481,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2513,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124938507</v>
+        <v>124939729</v>
       </c>
       <c r="B17" t="n">
-        <v>92098</v>
+        <v>98290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,34 +2529,48 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446376</v>
+        <v>446196</v>
       </c>
       <c r="R17" t="n">
-        <v>7023866</v>
+        <v>7023847</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2564,7 +2602,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2574,12 +2612,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,10 +2644,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124938916</v>
+        <v>124938507</v>
       </c>
       <c r="B18" t="n">
-        <v>56836</v>
+        <v>92098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2622,42 +2660,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446512</v>
+        <v>446376</v>
       </c>
       <c r="R18" t="n">
-        <v>7023807</v>
+        <v>7023866</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2686,7 +2719,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2696,7 +2729,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2711,22 +2749,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124940260</v>
+        <v>124938918</v>
       </c>
       <c r="B19" t="n">
-        <v>57793</v>
+        <v>95503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2735,50 +2773,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446210</v>
+        <v>446330</v>
       </c>
       <c r="R19" t="n">
-        <v>7023879</v>
+        <v>7023872</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2807,7 +2836,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2817,7 +2846,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2832,22 +2866,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124940176</v>
+        <v>124936204</v>
       </c>
       <c r="B20" t="n">
-        <v>79988</v>
+        <v>91184</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2856,41 +2890,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446236</v>
+        <v>446448</v>
       </c>
       <c r="R20" t="n">
-        <v>7023806</v>
+        <v>7023801</v>
       </c>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2919,7 +2967,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2929,7 +2977,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,10 +3009,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124935467</v>
+        <v>124939368</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
+        <v>92098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2968,35 +3021,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3005,13 +3058,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446385</v>
+        <v>446236</v>
       </c>
       <c r="R21" t="n">
-        <v>7023868</v>
+        <v>7023806</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3040,7 +3093,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3050,7 +3103,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3077,10 +3130,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124937619</v>
+        <v>124937775</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3089,35 +3142,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3126,10 +3179,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446452</v>
+        <v>446465</v>
       </c>
       <c r="R22" t="n">
-        <v>7023890</v>
+        <v>7023899</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3161,7 +3214,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3171,12 +3224,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3203,10 +3256,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124937775</v>
+        <v>124937346</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3215,50 +3268,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446465</v>
+        <v>446466</v>
       </c>
       <c r="R23" t="n">
-        <v>7023899</v>
+        <v>7023868</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3287,7 +3340,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3297,12 +3350,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3317,22 +3365,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124939441</v>
+        <v>124939668</v>
       </c>
       <c r="B24" t="n">
-        <v>95515</v>
+        <v>91162</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3341,25 +3389,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2813</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3369,13 +3417,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446204</v>
+        <v>446191</v>
       </c>
       <c r="R24" t="n">
-        <v>7023839</v>
+        <v>7023833</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3404,7 +3452,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3414,12 +3462,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i fuktig granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3446,10 +3494,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124940379</v>
+        <v>124938916</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3458,55 +3506,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446275</v>
+        <v>446512</v>
       </c>
       <c r="R25" t="n">
-        <v>7023902</v>
+        <v>7023807</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3535,7 +3574,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3545,12 +3584,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:44</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,22 +3599,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124935567</v>
+        <v>124938548</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
+        <v>58001</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3589,55 +3623,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446418</v>
+        <v>446512</v>
       </c>
       <c r="R26" t="n">
-        <v>7023888</v>
+        <v>7023807</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3666,7 +3695,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3676,12 +3705,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3696,7 +3720,7 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3708,10 +3732,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124936685</v>
+        <v>124935467</v>
       </c>
       <c r="B27" t="n">
-        <v>92098</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3720,38 +3744,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446500</v>
+        <v>446385</v>
       </c>
       <c r="R27" t="n">
-        <v>7023715</v>
+        <v>7023868</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3783,7 +3816,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3793,12 +3826,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3813,7 +3841,7 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3825,10 +3853,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124936966</v>
+        <v>124939540</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
+        <v>105278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3837,52 +3865,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446533</v>
+        <v>446196</v>
       </c>
       <c r="R28" t="n">
-        <v>7023754</v>
+        <v>7023833</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3914,7 +3928,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3924,12 +3938,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>+ 1 vinterståndare</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3944,19 +3958,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124940534</v>
+        <v>124936055</v>
       </c>
       <c r="B29" t="n">
         <v>98269</v>
@@ -3991,7 +4005,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4006,17 +4020,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446314</v>
+        <v>446414</v>
       </c>
       <c r="R29" t="n">
-        <v>7023930</v>
+        <v>7023792</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4045,7 +4059,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4055,7 +4069,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4070,22 +4089,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124936055</v>
+        <v>124939161</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4094,40 +4113,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4136,10 +4150,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446414</v>
+        <v>446288</v>
       </c>
       <c r="R30" t="n">
-        <v>7023792</v>
+        <v>7023859</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
@@ -4171,7 +4185,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4181,12 +4195,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4206,17 +4220,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124937355</v>
+        <v>124936198</v>
       </c>
       <c r="B31" t="n">
-        <v>98269</v>
+        <v>75025</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4225,52 +4239,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446493</v>
+        <v>446431</v>
       </c>
       <c r="R31" t="n">
-        <v>7023830</v>
+        <v>7023787</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4312,12 +4312,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4344,7 +4344,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124936198</v>
+        <v>124937238</v>
       </c>
       <c r="B32" t="n">
         <v>75025</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446431</v>
+        <v>446500</v>
       </c>
       <c r="R32" t="n">
-        <v>7023787</v>
+        <v>7023860</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4461,10 +4461,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124939729</v>
+        <v>124936966</v>
       </c>
       <c r="B33" t="n">
-        <v>98290</v>
+        <v>98269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4473,30 +4473,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4511,14 +4511,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446196</v>
+        <v>446533</v>
       </c>
       <c r="R33" t="n">
-        <v>7023847</v>
+        <v>7023754</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4580,19 +4580,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124937870</v>
+        <v>124940534</v>
       </c>
       <c r="B34" t="n">
         <v>98269</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4642,17 +4642,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446461</v>
+        <v>446314</v>
       </c>
       <c r="R34" t="n">
-        <v>7023883</v>
+        <v>7023930</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4691,12 +4691,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4711,22 +4706,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124937346</v>
+        <v>124940260</v>
       </c>
       <c r="B35" t="n">
-        <v>78947</v>
+        <v>57793</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4739,46 +4734,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446466</v>
+        <v>446210</v>
       </c>
       <c r="R35" t="n">
-        <v>7023868</v>
+        <v>7023879</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4807,7 +4802,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4817,7 +4812,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4844,7 +4839,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124939161</v>
+        <v>124936862</v>
       </c>
       <c r="B36" t="n">
         <v>78947</v>
@@ -4877,29 +4872,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446288</v>
+        <v>446512</v>
       </c>
       <c r="R36" t="n">
-        <v>7023859</v>
+        <v>7023771</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4928,7 +4914,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4938,12 +4924,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4963,17 +4949,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124937179</v>
+        <v>124938398</v>
       </c>
       <c r="B37" t="n">
-        <v>77879</v>
+        <v>100451</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4982,38 +4968,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446500</v>
+        <v>446403</v>
       </c>
       <c r="R37" t="n">
-        <v>7023860</v>
+        <v>7023878</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -3130,10 +3130,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124937775</v>
+        <v>124937346</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3142,50 +3142,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446465</v>
+        <v>446466</v>
       </c>
       <c r="R22" t="n">
-        <v>7023899</v>
+        <v>7023868</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3224,12 +3224,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3244,22 +3239,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124937346</v>
+        <v>124939668</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
+        <v>91162</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3272,46 +3267,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446466</v>
+        <v>446191</v>
       </c>
       <c r="R23" t="n">
-        <v>7023868</v>
+        <v>7023833</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3340,7 +3326,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3350,7 +3336,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3365,22 +3356,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124939668</v>
+        <v>124938916</v>
       </c>
       <c r="B24" t="n">
-        <v>91162</v>
+        <v>56836</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3389,41 +3380,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446191</v>
+        <v>446512</v>
       </c>
       <c r="R24" t="n">
-        <v>7023833</v>
+        <v>7023807</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3452,7 +3448,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3462,12 +3458,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3482,22 +3473,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124938916</v>
+        <v>124937775</v>
       </c>
       <c r="B25" t="n">
-        <v>56836</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3506,46 +3497,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446512</v>
+        <v>446465</v>
       </c>
       <c r="R25" t="n">
-        <v>7023807</v>
+        <v>7023899</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3574,7 +3569,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3584,7 +3579,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3599,12 +3599,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124940534</v>
+        <v>124940260</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
+        <v>57793</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4604,55 +4604,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446314</v>
+        <v>446210</v>
       </c>
       <c r="R34" t="n">
-        <v>7023930</v>
+        <v>7023879</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4681,7 +4676,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4691,7 +4686,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4718,10 +4713,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124940260</v>
+        <v>124940534</v>
       </c>
       <c r="B35" t="n">
-        <v>57793</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4730,50 +4725,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446210</v>
+        <v>446314</v>
       </c>
       <c r="R35" t="n">
-        <v>7023879</v>
+        <v>7023930</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -3130,10 +3130,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124937346</v>
+        <v>124938916</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3142,35 +3142,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3179,10 +3175,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446466</v>
+        <v>446512</v>
       </c>
       <c r="R22" t="n">
-        <v>7023868</v>
+        <v>7023807</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3214,7 +3210,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3224,7 +3220,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,10 +3247,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124939668</v>
+        <v>124937775</v>
       </c>
       <c r="B23" t="n">
-        <v>91162</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3263,38 +3259,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446191</v>
+        <v>446465</v>
       </c>
       <c r="R23" t="n">
-        <v>7023833</v>
+        <v>7023899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3326,7 +3331,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3336,12 +3341,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3368,10 +3373,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124938916</v>
+        <v>124937346</v>
       </c>
       <c r="B24" t="n">
-        <v>56836</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3380,31 +3385,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3413,10 +3422,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446512</v>
+        <v>446466</v>
       </c>
       <c r="R24" t="n">
-        <v>7023807</v>
+        <v>7023868</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3448,7 +3457,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3458,7 +3467,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3485,10 +3494,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124937775</v>
+        <v>124939668</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
+        <v>91162</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3497,47 +3506,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446465</v>
+        <v>446191</v>
       </c>
       <c r="R25" t="n">
-        <v>7023899</v>
+        <v>7023833</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 40143-2023 artfynd.xlsx
+++ b/artfynd/A 40143-2023 artfynd.xlsx
@@ -675,53 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124940176</v>
+        <v>124940379</v>
       </c>
       <c r="B2" t="n">
-        <v>79988</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446236</v>
+        <v>446275</v>
       </c>
       <c r="R2" t="n">
-        <v>7023806</v>
+        <v>7023902</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +789,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -792,11 +806,6 @@
       <c r="B3" t="n">
         <v>95515</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>LC</t>
@@ -904,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124937619</v>
+        <v>124940260</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,46 +924,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446452</v>
+        <v>446210</v>
       </c>
       <c r="R4" t="n">
-        <v>7023890</v>
+        <v>7023879</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,27 +1017,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124936685</v>
+        <v>124939540</v>
       </c>
       <c r="B5" t="n">
-        <v>92098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446500</v>
+        <v>446196</v>
       </c>
       <c r="R5" t="n">
-        <v>7023715</v>
+        <v>7023833</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1109,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,16 +1141,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124937355</v>
+        <v>124939030</v>
       </c>
       <c r="B6" t="n">
         <v>98269</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1182,7 +1171,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1197,14 +1186,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446493</v>
+        <v>446512</v>
       </c>
       <c r="R6" t="n">
-        <v>7023830</v>
+        <v>7023807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,12 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog, glest, fuktig mark</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,62 +1250,71 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937179</v>
+        <v>124936966</v>
       </c>
       <c r="B7" t="n">
-        <v>77879</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446500</v>
+        <v>446533</v>
       </c>
       <c r="R7" t="n">
-        <v>7023860</v>
+        <v>7023754</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,12 +1356,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
+          <t>+ 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,54 +1376,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939030</v>
+        <v>124939729</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1445,14 +1433,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446512</v>
+        <v>446196</v>
       </c>
       <c r="R8" t="n">
-        <v>7023807</v>
+        <v>7023847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,79 +1502,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937870</v>
+        <v>124939368</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446461</v>
+        <v>446236</v>
       </c>
       <c r="R9" t="n">
-        <v>7023883</v>
+        <v>7023806</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,12 +1603,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,27 +1618,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939565</v>
+        <v>124938548</v>
       </c>
       <c r="B10" t="n">
-        <v>91860</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58001</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,37 +1641,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446214</v>
+        <v>446512</v>
       </c>
       <c r="R10" t="n">
-        <v>7023841</v>
+        <v>7023807</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1727,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1737,12 +1719,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,62 +1734,71 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937032</v>
+        <v>124937870</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446505</v>
+        <v>446461</v>
       </c>
       <c r="R11" t="n">
-        <v>7023805</v>
+        <v>7023883</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,12 +1840,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1886,53 +1872,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937224</v>
+        <v>124940176</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446500</v>
+        <v>446236</v>
       </c>
       <c r="R12" t="n">
-        <v>7023860</v>
+        <v>7023806</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1961,7 +1942,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1971,12 +1952,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,79 +1967,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124940379</v>
+        <v>124937346</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446275</v>
+        <v>446466</v>
       </c>
       <c r="R13" t="n">
-        <v>7023902</v>
+        <v>7023868</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2068,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:44</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog på fuktig mark</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2122,79 +2083,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124935567</v>
+        <v>124936198</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75025</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446418</v>
+        <v>446431</v>
       </c>
       <c r="R14" t="n">
-        <v>7023888</v>
+        <v>7023787</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2223,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,12 +2175,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2258,74 +2200,60 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124937577</v>
+        <v>124938916</v>
       </c>
       <c r="B15" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446475</v>
+        <v>446512</v>
       </c>
       <c r="R15" t="n">
-        <v>7023891</v>
+        <v>7023807</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2354,7 +2282,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2364,12 +2292,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog på fuktig mark</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2384,65 +2307,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124940281</v>
+        <v>124935467</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446268</v>
+        <v>446385</v>
       </c>
       <c r="R16" t="n">
-        <v>7023890</v>
+        <v>7023868</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2471,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2481,12 +2408,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog på fuktig mark</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2501,64 +2423,54 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124939729</v>
+        <v>124937619</v>
       </c>
       <c r="B17" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2567,10 +2479,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446196</v>
+        <v>446452</v>
       </c>
       <c r="R17" t="n">
-        <v>7023847</v>
+        <v>7023890</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2602,7 +2514,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2612,12 +2524,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2644,37 +2556,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124938507</v>
+        <v>124936862</v>
       </c>
       <c r="B18" t="n">
-        <v>92098</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2684,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446376</v>
+        <v>446512</v>
       </c>
       <c r="R18" t="n">
-        <v>7023866</v>
+        <v>7023771</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2719,7 +2626,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2729,12 +2636,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2754,44 +2661,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124938918</v>
+        <v>124937032</v>
       </c>
       <c r="B19" t="n">
-        <v>95503</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2801,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446330</v>
+        <v>446505</v>
       </c>
       <c r="R19" t="n">
-        <v>7023872</v>
+        <v>7023805</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2836,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2846,12 +2748,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i fuktstråk i äldre barrblandskog</t>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2878,67 +2780,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124936204</v>
+        <v>124936055</v>
       </c>
       <c r="B20" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446448</v>
+        <v>446414</v>
       </c>
       <c r="R20" t="n">
-        <v>7023801</v>
+        <v>7023792</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2967,7 +2864,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2977,12 +2874,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2997,59 +2894,59 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124939368</v>
+        <v>124940534</v>
       </c>
       <c r="B21" t="n">
-        <v>92098</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3058,13 +2955,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446236</v>
+        <v>446314</v>
       </c>
       <c r="R21" t="n">
-        <v>7023806</v>
+        <v>7023930</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3093,7 +2990,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3103,7 +3000,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3130,58 +3027,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124938916</v>
+        <v>124937179</v>
       </c>
       <c r="B22" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446512</v>
+        <v>446500</v>
       </c>
       <c r="R22" t="n">
-        <v>7023807</v>
+        <v>7023860</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3210,7 +3097,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3220,7 +3107,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På rejält gammal gran i gammal gles fuktig granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3235,7 +3127,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3247,59 +3139,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124937775</v>
+        <v>124939668</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446465</v>
+        <v>446191</v>
       </c>
       <c r="R23" t="n">
-        <v>7023899</v>
+        <v>7023833</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3331,7 +3209,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3341,12 +3219,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3373,62 +3251,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124937346</v>
+        <v>124938507</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446466</v>
+        <v>446376</v>
       </c>
       <c r="R24" t="n">
-        <v>7023868</v>
+        <v>7023866</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3457,7 +3321,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3467,7 +3331,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3482,27 +3351,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124939668</v>
+        <v>124936204</v>
       </c>
       <c r="B25" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3510,37 +3374,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Jmt</t>
+          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446191</v>
+        <v>446448</v>
       </c>
       <c r="R25" t="n">
-        <v>7023833</v>
+        <v>7023801</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3569,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3579,12 +3457,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3599,7 +3477,7 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3611,15 +3489,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124938548</v>
+        <v>124939565</v>
       </c>
       <c r="B26" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91860</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3627,46 +3500,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446512</v>
+        <v>446214</v>
       </c>
       <c r="R26" t="n">
-        <v>7023807</v>
+        <v>7023841</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3695,7 +3559,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3705,7 +3569,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3720,7 +3589,7 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3732,42 +3601,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124935467</v>
+        <v>124938398</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3775,16 +3639,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446385</v>
+        <v>446403</v>
       </c>
       <c r="R27" t="n">
-        <v>7023868</v>
+        <v>7023878</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3816,7 +3685,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3826,7 +3695,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På marken i fuktig gles blandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3841,7 +3715,7 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3853,15 +3727,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124939540</v>
+        <v>124936685</v>
       </c>
       <c r="B28" t="n">
-        <v>105278</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92098</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3869,21 +3738,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3893,10 +3762,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446196</v>
+        <v>446500</v>
       </c>
       <c r="R28" t="n">
-        <v>7023833</v>
+        <v>7023715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3928,7 +3797,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3938,12 +3807,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3970,52 +3839,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124936055</v>
+        <v>124939161</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4024,10 +3883,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446414</v>
+        <v>446288</v>
       </c>
       <c r="R29" t="n">
-        <v>7023792</v>
+        <v>7023859</v>
       </c>
       <c r="S29" t="n">
         <v>7</v>
@@ -4059,7 +3918,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4069,12 +3928,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>12 plantor på marken i äldre granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4101,16 +3960,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124939161</v>
+        <v>124940281</v>
       </c>
       <c r="B30" t="n">
         <v>78947</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4134,26 +3988,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446288</v>
+        <v>446268</v>
       </c>
       <c r="R30" t="n">
-        <v>7023859</v>
+        <v>7023890</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
@@ -4185,7 +4030,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4195,7 +4040,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4227,50 +4072,59 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124936198</v>
+        <v>124937355</v>
       </c>
       <c r="B31" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446431</v>
+        <v>446493</v>
       </c>
       <c r="R31" t="n">
-        <v>7023787</v>
+        <v>7023830</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4302,7 +4156,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4312,12 +4166,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På marken i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4344,37 +4198,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124937238</v>
+        <v>124938918</v>
       </c>
       <c r="B32" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95503</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4384,10 +4233,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446500</v>
+        <v>446330</v>
       </c>
       <c r="R32" t="n">
-        <v>7023860</v>
+        <v>7023872</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4268,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4429,12 +4278,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i fuktstråk i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4461,64 +4310,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124936966</v>
+        <v>124937238</v>
       </c>
       <c r="B33" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75025</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446533</v>
+        <v>446500</v>
       </c>
       <c r="R33" t="n">
-        <v>7023754</v>
+        <v>7023860</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4550,7 +4380,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4560,12 +4390,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>+ 1 vinterståndare</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4580,74 +4410,74 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124940260</v>
+        <v>124935567</v>
       </c>
       <c r="B34" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åslägden, Åslägden, Mattmar, Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446210</v>
+        <v>446418</v>
       </c>
       <c r="R34" t="n">
-        <v>7023879</v>
+        <v>7023888</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4676,7 +4506,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4686,7 +4516,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog, bördigt, rikligt med kransmossa runtom</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4701,28 +4536,23 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124940534</v>
+        <v>124937577</v>
       </c>
       <c r="B35" t="n">
         <v>98269</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>VU</t>
@@ -4748,7 +4578,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4763,17 +4593,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åsläggden norr om , Åsläggden norr om , Jmt</t>
+          <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446314</v>
+        <v>446475</v>
       </c>
       <c r="R35" t="n">
-        <v>7023930</v>
+        <v>7023891</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4802,7 +4632,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4812,7 +4642,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4827,28 +4662,23 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124936862</v>
+        <v>124937224</v>
       </c>
       <c r="B36" t="n">
         <v>78947</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4879,10 +4709,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446512</v>
+        <v>446500</v>
       </c>
       <c r="R36" t="n">
-        <v>7023771</v>
+        <v>7023860</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4914,7 +4744,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4924,12 +4754,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På gammal gran i gammal granskog, glest, fuktig mark</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4949,49 +4779,44 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124938398</v>
+        <v>124937775</v>
       </c>
       <c r="B37" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4999,21 +4824,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åslägden, Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446403</v>
+        <v>446465</v>
       </c>
       <c r="R37" t="n">
-        <v>7023878</v>
+        <v>7023899</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5045,7 +4865,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5055,12 +4875,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På marken i fuktig gles blandskog</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
